--- a/research/traditional_assets/database/data/colombia/colombia_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_precious_metals.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.116943001039595</v>
+        <v>0.1165629505359564</v>
       </c>
       <c r="C2">
-        <v>314.6981344764595</v>
+        <v>312.1648427110201</v>
       </c>
       <c r="D2">
-        <v>257.5981344764595</v>
+        <v>258.2468427110201</v>
       </c>
       <c r="E2">
-        <v>-28.7</v>
+        <v>-25.518</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.182</v>
       </c>
       <c r="G2">
         <v>57.1</v>
@@ -1451,28 +1451,28 @@
         <v>140.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1600546</v>
       </c>
       <c r="N2">
-        <v>140.4</v>
+        <v>140.2399454</v>
       </c>
       <c r="O2">
-        <v>49.14</v>
+        <v>49.08398089</v>
       </c>
       <c r="P2">
-        <v>91.26000000000001</v>
+        <v>91.15596451000002</v>
       </c>
       <c r="Q2">
-        <v>150.76</v>
+        <v>150.65596451</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.116943001039595</v>
+        <v>0.1174101015514711</v>
       </c>
       <c r="T2">
-        <v>1.035217350236429</v>
+        <v>1.042014231828891</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>877.200655276387</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1165629505359564</v>
+        <v>0.1161829000323178</v>
       </c>
       <c r="C3">
-        <v>312.1648427110201</v>
+        <v>309.6348264724401</v>
       </c>
       <c r="D3">
-        <v>258.2468427110201</v>
+        <v>258.89882647244</v>
       </c>
       <c r="E3">
-        <v>-25.518</v>
+        <v>-22.336</v>
       </c>
       <c r="F3">
-        <v>3.182</v>
+        <v>6.364</v>
       </c>
       <c r="G3">
         <v>57.1</v>
@@ -1533,28 +1533,28 @@
         <v>140.4</v>
       </c>
       <c r="M3">
-        <v>0.1600546</v>
+        <v>0.3201092</v>
       </c>
       <c r="N3">
-        <v>140.2399454</v>
+        <v>140.0798908</v>
       </c>
       <c r="O3">
-        <v>49.08398089</v>
+        <v>49.02796178000001</v>
       </c>
       <c r="P3">
-        <v>91.15596451000002</v>
+        <v>91.05192902000002</v>
       </c>
       <c r="Q3">
-        <v>150.65596451</v>
+        <v>150.55192902</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1174101015514711</v>
+        <v>0.1178867347268549</v>
       </c>
       <c r="T3">
-        <v>1.042014231828891</v>
+        <v>1.048949825290586</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>877.200655276387</v>
+        <v>438.6003276381936</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1161829000323178</v>
+        <v>0.1158028495286792</v>
       </c>
       <c r="C4">
-        <v>309.6348264724401</v>
+        <v>307.1081106322212</v>
       </c>
       <c r="D4">
-        <v>258.89882647244</v>
+        <v>259.5541106322212</v>
       </c>
       <c r="E4">
-        <v>-22.336</v>
+        <v>-19.154</v>
       </c>
       <c r="F4">
-        <v>6.364</v>
+        <v>9.545999999999999</v>
       </c>
       <c r="G4">
         <v>57.1</v>
@@ -1615,28 +1615,28 @@
         <v>140.4</v>
       </c>
       <c r="M4">
-        <v>0.3201092</v>
+        <v>0.4801637999999999</v>
       </c>
       <c r="N4">
-        <v>140.0798908</v>
+        <v>139.9198362</v>
       </c>
       <c r="O4">
-        <v>49.02796178000001</v>
+        <v>48.97194267</v>
       </c>
       <c r="P4">
-        <v>91.05192902000002</v>
+        <v>90.94789352999999</v>
       </c>
       <c r="Q4">
-        <v>150.55192902</v>
+        <v>150.44789353</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1178867347268549</v>
+        <v>0.1183731953903909</v>
       </c>
       <c r="T4">
-        <v>1.048949825290586</v>
+        <v>1.056028420679326</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>438.6003276381936</v>
+        <v>292.4002184254624</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1158028495286792</v>
+        <v>0.1154227990250406</v>
       </c>
       <c r="C5">
-        <v>307.1081106322212</v>
+        <v>304.5847203143074</v>
       </c>
       <c r="D5">
-        <v>259.5541106322212</v>
+        <v>260.2127203143074</v>
       </c>
       <c r="E5">
-        <v>-19.154</v>
+        <v>-15.972</v>
       </c>
       <c r="F5">
-        <v>9.545999999999999</v>
+        <v>12.728</v>
       </c>
       <c r="G5">
         <v>57.1</v>
@@ -1697,28 +1697,28 @@
         <v>140.4</v>
       </c>
       <c r="M5">
-        <v>0.4801637999999999</v>
+        <v>0.6402184</v>
       </c>
       <c r="N5">
-        <v>139.9198362</v>
+        <v>139.7597816</v>
       </c>
       <c r="O5">
-        <v>48.97194267</v>
+        <v>48.91592356</v>
       </c>
       <c r="P5">
-        <v>90.94789352999999</v>
+        <v>90.84385804</v>
       </c>
       <c r="Q5">
-        <v>150.44789353</v>
+        <v>150.34385804</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1183731953903909</v>
+        <v>0.118869790651084</v>
       </c>
       <c r="T5">
-        <v>1.056028420679326</v>
+        <v>1.063254486805332</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>292.4002184254624</v>
+        <v>219.3001638190968</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1154227990250406</v>
+        <v>0.115042748521402</v>
       </c>
       <c r="C6">
-        <v>304.5847203143074</v>
+        <v>302.0646808982962</v>
       </c>
       <c r="D6">
-        <v>260.2127203143074</v>
+        <v>260.8746808982962</v>
       </c>
       <c r="E6">
-        <v>-15.972</v>
+        <v>-12.79</v>
       </c>
       <c r="F6">
-        <v>12.728</v>
+        <v>15.91</v>
       </c>
       <c r="G6">
         <v>57.1</v>
@@ -1779,28 +1779,28 @@
         <v>140.4</v>
       </c>
       <c r="M6">
-        <v>0.6402184</v>
+        <v>0.800273</v>
       </c>
       <c r="N6">
-        <v>139.7597816</v>
+        <v>139.599727</v>
       </c>
       <c r="O6">
-        <v>48.91592356</v>
+        <v>48.85990444999999</v>
       </c>
       <c r="P6">
-        <v>90.84385804</v>
+        <v>90.73982255000001</v>
       </c>
       <c r="Q6">
-        <v>150.34385804</v>
+        <v>150.23982255</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.118869790651084</v>
+        <v>0.1193768405488443</v>
       </c>
       <c r="T6">
-        <v>1.063254486805332</v>
+        <v>1.070632680639254</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>219.3001638190968</v>
+        <v>175.4401310552774</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.115042748521402</v>
+        <v>0.1146626980177635</v>
       </c>
       <c r="C7">
-        <v>302.0646808982962</v>
+        <v>299.5480180226981</v>
       </c>
       <c r="D7">
-        <v>260.8746808982962</v>
+        <v>261.5400180226981</v>
       </c>
       <c r="E7">
-        <v>-12.79</v>
+        <v>-9.607999999999997</v>
       </c>
       <c r="F7">
-        <v>15.91</v>
+        <v>19.092</v>
       </c>
       <c r="G7">
         <v>57.1</v>
@@ -1861,28 +1861,28 @@
         <v>140.4</v>
       </c>
       <c r="M7">
-        <v>0.800273</v>
+        <v>0.9603276000000001</v>
       </c>
       <c r="N7">
-        <v>139.599727</v>
+        <v>139.4396724</v>
       </c>
       <c r="O7">
-        <v>48.85990444999999</v>
+        <v>48.80388534</v>
       </c>
       <c r="P7">
-        <v>90.73982255000001</v>
+        <v>90.63578706000001</v>
       </c>
       <c r="Q7">
-        <v>150.23982255</v>
+        <v>150.13578706</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1193768405488443</v>
+        <v>0.1198946787423016</v>
       </c>
       <c r="T7">
-        <v>1.070632680639254</v>
+        <v>1.078167857320707</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>175.4401310552774</v>
+        <v>146.2001092127311</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1146626980177635</v>
+        <v>0.1142826475141249</v>
       </c>
       <c r="C8">
-        <v>299.5480180226981</v>
+        <v>297.0347575882475</v>
       </c>
       <c r="D8">
-        <v>261.5400180226981</v>
+        <v>262.2087575882475</v>
       </c>
       <c r="E8">
-        <v>-9.608000000000001</v>
+        <v>-6.426000000000002</v>
       </c>
       <c r="F8">
-        <v>19.092</v>
+        <v>22.274</v>
       </c>
       <c r="G8">
         <v>57.1</v>
@@ -1943,28 +1943,28 @@
         <v>140.4</v>
       </c>
       <c r="M8">
-        <v>0.9603275999999998</v>
+        <v>1.1203822</v>
       </c>
       <c r="N8">
-        <v>139.4396724</v>
+        <v>139.2796178</v>
       </c>
       <c r="O8">
-        <v>48.80388534</v>
+        <v>48.74786623</v>
       </c>
       <c r="P8">
-        <v>90.63578706000001</v>
+        <v>90.53175157000001</v>
       </c>
       <c r="Q8">
-        <v>150.13578706</v>
+        <v>150.03175157</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1198946787423016</v>
+        <v>0.1204236532409945</v>
       </c>
       <c r="T8">
-        <v>1.078167857320707</v>
+        <v>1.085865080812512</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>146.2001092127312</v>
+        <v>125.3143793251982</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1142826475141249</v>
+        <v>0.1139025970104863</v>
       </c>
       <c r="C9">
-        <v>297.0347575882475</v>
+        <v>294.5249257612633</v>
       </c>
       <c r="D9">
-        <v>262.2087575882475</v>
+        <v>262.8809257612633</v>
       </c>
       <c r="E9">
-        <v>-6.425999999999998</v>
+        <v>-3.244</v>
       </c>
       <c r="F9">
-        <v>22.274</v>
+        <v>25.456</v>
       </c>
       <c r="G9">
         <v>57.1</v>
@@ -2025,28 +2025,28 @@
         <v>140.4</v>
       </c>
       <c r="M9">
-        <v>1.1203822</v>
+        <v>1.2804368</v>
       </c>
       <c r="N9">
-        <v>139.2796178</v>
+        <v>139.1195632</v>
       </c>
       <c r="O9">
-        <v>48.74786623</v>
+        <v>48.69184712000001</v>
       </c>
       <c r="P9">
-        <v>90.53175157000001</v>
+        <v>90.42771608000001</v>
       </c>
       <c r="Q9">
-        <v>150.03175157</v>
+        <v>149.92771608</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1204236532409945</v>
+        <v>0.1209641271853112</v>
       </c>
       <c r="T9">
-        <v>1.085865080812512</v>
+        <v>1.093729635249792</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>125.3143793251982</v>
+        <v>109.6500819095484</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1139025970104863</v>
+        <v>0.1135225465068477</v>
       </c>
       <c r="C10">
-        <v>294.5249257612633</v>
+        <v>292.0185489770616</v>
       </c>
       <c r="D10">
-        <v>262.8809257612633</v>
+        <v>263.5565489770615</v>
       </c>
       <c r="E10">
-        <v>-3.244</v>
+        <v>-0.06200000000000117</v>
       </c>
       <c r="F10">
-        <v>25.456</v>
+        <v>28.638</v>
       </c>
       <c r="G10">
         <v>57.1</v>
@@ -2107,28 +2107,28 @@
         <v>140.4</v>
       </c>
       <c r="M10">
-        <v>1.2804368</v>
+        <v>1.4404914</v>
       </c>
       <c r="N10">
-        <v>139.1195632</v>
+        <v>138.9595086</v>
       </c>
       <c r="O10">
-        <v>48.69184712000001</v>
+        <v>48.63582801</v>
       </c>
       <c r="P10">
-        <v>90.42771608000001</v>
+        <v>90.32368059</v>
       </c>
       <c r="Q10">
-        <v>149.92771608</v>
+        <v>149.82368059</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1209641271853112</v>
+        <v>0.1215164796778546</v>
       </c>
       <c r="T10">
-        <v>1.093729635249792</v>
+        <v>1.101767037037342</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>109.6500819095484</v>
+        <v>97.46673947515411</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1135225465068477</v>
+        <v>0.1131424960032091</v>
       </c>
       <c r="C11">
-        <v>292.0185489770616</v>
+        <v>289.5156539434217</v>
       </c>
       <c r="D11">
-        <v>263.5565489770615</v>
+        <v>264.2356539434217</v>
       </c>
       <c r="E11">
-        <v>-0.06200000000000117</v>
+        <v>3.119999999999997</v>
       </c>
       <c r="F11">
-        <v>28.638</v>
+        <v>31.82</v>
       </c>
       <c r="G11">
         <v>57.1</v>
@@ -2189,28 +2189,28 @@
         <v>140.4</v>
       </c>
       <c r="M11">
-        <v>1.4404914</v>
+        <v>1.600546</v>
       </c>
       <c r="N11">
-        <v>138.9595086</v>
+        <v>138.799454</v>
       </c>
       <c r="O11">
-        <v>48.63582801</v>
+        <v>48.5798089</v>
       </c>
       <c r="P11">
-        <v>90.32368059</v>
+        <v>90.21964510000001</v>
       </c>
       <c r="Q11">
-        <v>149.82368059</v>
+        <v>149.7196451</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1215164796778546</v>
+        <v>0.1220811066702324</v>
       </c>
       <c r="T11">
-        <v>1.101767037037342</v>
+        <v>1.109983047753504</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>97.46673947515411</v>
+        <v>87.7200655276387</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1131424960032091</v>
+        <v>0.1127624454995706</v>
       </c>
       <c r="C12">
-        <v>289.5156539434217</v>
+        <v>287.0162676441051</v>
       </c>
       <c r="D12">
-        <v>264.2356539434217</v>
+        <v>264.9182676441051</v>
       </c>
       <c r="E12">
-        <v>3.120000000000001</v>
+        <v>6.302000000000003</v>
       </c>
       <c r="F12">
-        <v>31.82</v>
+        <v>35.002</v>
       </c>
       <c r="G12">
         <v>57.1</v>
@@ -2271,28 +2271,28 @@
         <v>140.4</v>
       </c>
       <c r="M12">
-        <v>1.600546</v>
+        <v>1.7606006</v>
       </c>
       <c r="N12">
-        <v>138.799454</v>
+        <v>138.6393994</v>
       </c>
       <c r="O12">
-        <v>48.5798089</v>
+        <v>48.52378979</v>
       </c>
       <c r="P12">
-        <v>90.21964510000001</v>
+        <v>90.11560961000001</v>
       </c>
       <c r="Q12">
-        <v>149.7196451</v>
+        <v>149.61560961</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1220811066702324</v>
+        <v>0.1226584219096298</v>
       </c>
       <c r="T12">
-        <v>1.109983047753504</v>
+        <v>1.118383687923962</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>87.7200655276387</v>
+        <v>79.74551411603517</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1127624454995706</v>
+        <v>0.112382394995932</v>
       </c>
       <c r="C13">
-        <v>287.0162676441051</v>
+        <v>284.5204173424303</v>
       </c>
       <c r="D13">
-        <v>264.9182676441051</v>
+        <v>265.6044173424303</v>
       </c>
       <c r="E13">
-        <v>6.302000000000003</v>
+        <v>9.483999999999998</v>
       </c>
       <c r="F13">
-        <v>35.002</v>
+        <v>38.184</v>
       </c>
       <c r="G13">
         <v>57.1</v>
@@ -2353,28 +2353,28 @@
         <v>140.4</v>
       </c>
       <c r="M13">
-        <v>1.7606006</v>
+        <v>1.9206552</v>
       </c>
       <c r="N13">
-        <v>138.6393994</v>
+        <v>138.4793448</v>
       </c>
       <c r="O13">
-        <v>48.52378979</v>
+        <v>48.46777068</v>
       </c>
       <c r="P13">
-        <v>90.11560961000001</v>
+        <v>90.01157412000001</v>
       </c>
       <c r="Q13">
-        <v>149.61560961</v>
+        <v>149.51157412</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1226584219096298</v>
+        <v>0.1232488579499227</v>
       </c>
       <c r="T13">
-        <v>1.118383687923962</v>
+        <v>1.126975251734658</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>79.74551411603517</v>
+        <v>73.10005460636559</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.112382394995932</v>
+        <v>0.1120023444922934</v>
       </c>
       <c r="C14">
-        <v>284.5204173424303</v>
+        <v>282.0281305849012</v>
       </c>
       <c r="D14">
-        <v>265.6044173424303</v>
+        <v>266.2941305849012</v>
       </c>
       <c r="E14">
-        <v>9.483999999999998</v>
+        <v>12.666</v>
       </c>
       <c r="F14">
-        <v>38.184</v>
+        <v>41.366</v>
       </c>
       <c r="G14">
         <v>57.1</v>
@@ -2435,28 +2435,28 @@
         <v>140.4</v>
       </c>
       <c r="M14">
-        <v>1.9206552</v>
+        <v>2.0807098</v>
       </c>
       <c r="N14">
-        <v>138.4793448</v>
+        <v>138.3192902</v>
       </c>
       <c r="O14">
-        <v>48.46777068</v>
+        <v>48.41175157</v>
       </c>
       <c r="P14">
-        <v>90.01157412000001</v>
+        <v>89.90753863</v>
       </c>
       <c r="Q14">
-        <v>149.51157412</v>
+        <v>149.40753863</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1232488579499227</v>
+        <v>0.1238528672325211</v>
       </c>
       <c r="T14">
-        <v>1.126975251734658</v>
+        <v>1.135764322759393</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>73.10005460636559</v>
+        <v>67.47697348279901</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1120023444922934</v>
+        <v>0.1116222939886548</v>
       </c>
       <c r="C15">
-        <v>282.0281305849012</v>
+        <v>279.5394352048945</v>
       </c>
       <c r="D15">
-        <v>266.2941305849012</v>
+        <v>266.9874352048945</v>
       </c>
       <c r="E15">
-        <v>12.666</v>
+        <v>15.848</v>
       </c>
       <c r="F15">
-        <v>41.366</v>
+        <v>44.548</v>
       </c>
       <c r="G15">
         <v>57.1</v>
@@ -2517,28 +2517,28 @@
         <v>140.4</v>
       </c>
       <c r="M15">
-        <v>2.0807098</v>
+        <v>2.2407644</v>
       </c>
       <c r="N15">
-        <v>138.3192902</v>
+        <v>138.1592356</v>
       </c>
       <c r="O15">
-        <v>48.41175157</v>
+        <v>48.35573246000001</v>
       </c>
       <c r="P15">
-        <v>89.90753863</v>
+        <v>89.80350314</v>
       </c>
       <c r="Q15">
-        <v>149.40753863</v>
+        <v>149.30350314</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1238528672325211</v>
+        <v>0.1244709232426219</v>
       </c>
       <c r="T15">
-        <v>1.135764322759393</v>
+        <v>1.144757790784702</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>67.47697348279901</v>
+        <v>62.65718966259908</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1116222939886548</v>
+        <v>0.1112422434850162</v>
       </c>
       <c r="C16">
-        <v>279.5394352048945</v>
+        <v>277.0543593264038</v>
       </c>
       <c r="D16">
-        <v>266.9874352048945</v>
+        <v>267.6843593264038</v>
       </c>
       <c r="E16">
-        <v>15.848</v>
+        <v>19.03</v>
       </c>
       <c r="F16">
-        <v>44.548</v>
+        <v>47.73</v>
       </c>
       <c r="G16">
         <v>57.1</v>
@@ -2599,28 +2599,28 @@
         <v>140.4</v>
       </c>
       <c r="M16">
-        <v>2.2407644</v>
+        <v>2.400819</v>
       </c>
       <c r="N16">
-        <v>138.1592356</v>
+        <v>137.999181</v>
       </c>
       <c r="O16">
-        <v>48.35573246000001</v>
+        <v>48.29971335</v>
       </c>
       <c r="P16">
-        <v>89.80350314</v>
+        <v>89.69946765</v>
       </c>
       <c r="Q16">
-        <v>149.30350314</v>
+        <v>149.19946765</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1244709232426219</v>
+        <v>0.1251035217470779</v>
       </c>
       <c r="T16">
-        <v>1.144757790784702</v>
+        <v>1.153962869822372</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>62.65718966259908</v>
+        <v>58.48004368509245</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1112422434850162</v>
+        <v>0.1108621929813776</v>
       </c>
       <c r="C17">
-        <v>277.0543593264038</v>
+        <v>274.5729313678421</v>
       </c>
       <c r="D17">
-        <v>267.6843593264038</v>
+        <v>268.3849313678421</v>
       </c>
       <c r="E17">
-        <v>19.03</v>
+        <v>22.212</v>
       </c>
       <c r="F17">
-        <v>47.73</v>
+        <v>50.912</v>
       </c>
       <c r="G17">
         <v>57.1</v>
@@ -2681,28 +2681,28 @@
         <v>140.4</v>
       </c>
       <c r="M17">
-        <v>2.400819</v>
+        <v>2.5608736</v>
       </c>
       <c r="N17">
-        <v>137.999181</v>
+        <v>137.8391264</v>
       </c>
       <c r="O17">
-        <v>48.29971335</v>
+        <v>48.24369424</v>
       </c>
       <c r="P17">
-        <v>89.69946765</v>
+        <v>89.59543216</v>
       </c>
       <c r="Q17">
-        <v>149.19946765</v>
+        <v>149.09543216</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1251035217470779</v>
+        <v>0.1257511821206877</v>
       </c>
       <c r="T17">
-        <v>1.153962869822372</v>
+        <v>1.163387117408558</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>58.48004368509246</v>
+        <v>54.82504095477419</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1108621929813776</v>
+        <v>0.110482142477739</v>
       </c>
       <c r="C18">
-        <v>274.5729313678421</v>
+        <v>272.0951800459049</v>
       </c>
       <c r="D18">
-        <v>268.3849313678421</v>
+        <v>269.0891800459049</v>
       </c>
       <c r="E18">
-        <v>22.212</v>
+        <v>25.394</v>
       </c>
       <c r="F18">
-        <v>50.912</v>
+        <v>54.094</v>
       </c>
       <c r="G18">
         <v>57.1</v>
@@ -2763,28 +2763,28 @@
         <v>140.4</v>
       </c>
       <c r="M18">
-        <v>2.5608736</v>
+        <v>2.7209282</v>
       </c>
       <c r="N18">
-        <v>137.8391264</v>
+        <v>137.6790718</v>
       </c>
       <c r="O18">
-        <v>48.24369424</v>
+        <v>48.18767513</v>
       </c>
       <c r="P18">
-        <v>89.59543216</v>
+        <v>89.49139667</v>
       </c>
       <c r="Q18">
-        <v>149.09543216</v>
+        <v>148.99139667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1257511821206877</v>
+        <v>0.1264144487683603</v>
       </c>
       <c r="T18">
-        <v>1.163387117408558</v>
+        <v>1.173038455298026</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>54.82504095477419</v>
+        <v>51.60003854566983</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.110482142477739</v>
+        <v>0.1101020919741005</v>
       </c>
       <c r="C19">
-        <v>272.0951800459049</v>
+        <v>269.621134379494</v>
       </c>
       <c r="D19">
-        <v>269.0891800459049</v>
+        <v>269.797134379494</v>
       </c>
       <c r="E19">
-        <v>25.394</v>
+        <v>28.576</v>
       </c>
       <c r="F19">
-        <v>54.094</v>
+        <v>57.276</v>
       </c>
       <c r="G19">
         <v>57.1</v>
@@ -2845,28 +2845,28 @@
         <v>140.4</v>
       </c>
       <c r="M19">
-        <v>2.7209282</v>
+        <v>2.8809828</v>
       </c>
       <c r="N19">
-        <v>137.6790718</v>
+        <v>137.5190172</v>
       </c>
       <c r="O19">
-        <v>48.18767513</v>
+        <v>48.13165602</v>
       </c>
       <c r="P19">
-        <v>89.49139667</v>
+        <v>89.38736118</v>
       </c>
       <c r="Q19">
-        <v>148.99139667</v>
+        <v>148.88736118</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1264144487683603</v>
+        <v>0.127093892651342</v>
       </c>
       <c r="T19">
-        <v>1.173038455298026</v>
+        <v>1.182925191672602</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>51.60003854566983</v>
+        <v>48.73336973757706</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1101020919741005</v>
+        <v>0.1097220414704619</v>
       </c>
       <c r="C20">
-        <v>269.621134379494</v>
+        <v>267.1508236937035</v>
       </c>
       <c r="D20">
-        <v>269.797134379494</v>
+        <v>270.5088236937035</v>
       </c>
       <c r="E20">
-        <v>28.576</v>
+        <v>31.758</v>
       </c>
       <c r="F20">
-        <v>57.276</v>
+        <v>60.458</v>
       </c>
       <c r="G20">
         <v>57.1</v>
@@ -2927,28 +2927,28 @@
         <v>140.4</v>
       </c>
       <c r="M20">
-        <v>2.8809828</v>
+        <v>3.0410374</v>
       </c>
       <c r="N20">
-        <v>137.5190172</v>
+        <v>137.3589626</v>
       </c>
       <c r="O20">
-        <v>48.13165602</v>
+        <v>48.07563691</v>
       </c>
       <c r="P20">
-        <v>89.38736118</v>
+        <v>89.28332569000001</v>
       </c>
       <c r="Q20">
-        <v>148.88736118</v>
+        <v>148.78332569</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.127093892651342</v>
+        <v>0.1277901129264962</v>
       </c>
       <c r="T20">
-        <v>1.182925191672602</v>
+        <v>1.193056044994699</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>48.73336973757706</v>
+        <v>46.16845554086248</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1097220414704619</v>
+        <v>0.1093419909668233</v>
       </c>
       <c r="C21">
-        <v>267.1508236937035</v>
+        <v>264.6842776238686</v>
       </c>
       <c r="D21">
-        <v>270.5088236937035</v>
+        <v>271.2242776238685</v>
       </c>
       <c r="E21">
-        <v>31.758</v>
+        <v>34.94</v>
       </c>
       <c r="F21">
-        <v>60.458</v>
+        <v>63.64</v>
       </c>
       <c r="G21">
         <v>57.1</v>
@@ -3009,28 +3009,28 @@
         <v>140.4</v>
       </c>
       <c r="M21">
-        <v>3.0410374</v>
+        <v>3.201092</v>
       </c>
       <c r="N21">
-        <v>137.3589626</v>
+        <v>137.198908</v>
       </c>
       <c r="O21">
-        <v>48.07563691</v>
+        <v>48.01961780000001</v>
       </c>
       <c r="P21">
-        <v>89.28332569000001</v>
+        <v>89.17929020000001</v>
       </c>
       <c r="Q21">
-        <v>148.78332569</v>
+        <v>148.6792902</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1277901129264962</v>
+        <v>0.1285037387085291</v>
       </c>
       <c r="T21">
-        <v>1.193056044994699</v>
+        <v>1.203440169649849</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>46.16845554086248</v>
+        <v>43.86003276381935</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1093419909668233</v>
+        <v>0.1089619404631847</v>
       </c>
       <c r="C22">
-        <v>264.6842776238686</v>
+        <v>262.2215261196795</v>
       </c>
       <c r="D22">
-        <v>271.2242776238685</v>
+        <v>271.9435261196795</v>
       </c>
       <c r="E22">
-        <v>34.94</v>
+        <v>38.122</v>
       </c>
       <c r="F22">
-        <v>63.64</v>
+        <v>66.822</v>
       </c>
       <c r="G22">
         <v>57.1</v>
@@ -3091,28 +3091,28 @@
         <v>140.4</v>
       </c>
       <c r="M22">
-        <v>3.201092</v>
+        <v>3.3611466</v>
       </c>
       <c r="N22">
-        <v>137.198908</v>
+        <v>137.0388534</v>
       </c>
       <c r="O22">
-        <v>48.01961780000001</v>
+        <v>47.96359869</v>
       </c>
       <c r="P22">
-        <v>89.17929020000001</v>
+        <v>89.07525471</v>
       </c>
       <c r="Q22">
-        <v>148.6792902</v>
+        <v>148.57525471</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1285037387085291</v>
+        <v>0.1292354309660566</v>
       </c>
       <c r="T22">
-        <v>1.203440169649849</v>
+        <v>1.214087183536774</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>43.86003276381935</v>
+        <v>41.77145977506604</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1089619404631847</v>
+        <v>0.1085818899595462</v>
       </c>
       <c r="C23">
-        <v>262.2215261196795</v>
+        <v>259.7625994493606</v>
       </c>
       <c r="D23">
-        <v>271.9435261196795</v>
+        <v>272.6665994493606</v>
       </c>
       <c r="E23">
-        <v>38.12199999999999</v>
+        <v>41.304</v>
       </c>
       <c r="F23">
-        <v>66.82199999999999</v>
+        <v>70.004</v>
       </c>
       <c r="G23">
         <v>57.1</v>
@@ -3173,28 +3173,28 @@
         <v>140.4</v>
       </c>
       <c r="M23">
-        <v>3.361146599999999</v>
+        <v>3.5212012</v>
       </c>
       <c r="N23">
-        <v>137.0388534</v>
+        <v>136.8787988</v>
       </c>
       <c r="O23">
-        <v>47.96359869</v>
+        <v>47.90757958</v>
       </c>
       <c r="P23">
-        <v>89.07525471</v>
+        <v>88.97121921999999</v>
       </c>
       <c r="Q23">
-        <v>148.57525471</v>
+        <v>148.47121922</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1292354309660566</v>
+        <v>0.1299858845635207</v>
       </c>
       <c r="T23">
-        <v>1.214087183536774</v>
+        <v>1.225007197779774</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>41.77145977506605</v>
+        <v>39.87275705801758</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1085818899595462</v>
+        <v>0.1082018394559076</v>
       </c>
       <c r="C24">
-        <v>259.7625994493606</v>
+        <v>257.3075282039163</v>
       </c>
       <c r="D24">
-        <v>272.6665994493606</v>
+        <v>273.3935282039163</v>
       </c>
       <c r="E24">
-        <v>41.304</v>
+        <v>44.486</v>
       </c>
       <c r="F24">
-        <v>70.004</v>
+        <v>73.18600000000001</v>
       </c>
       <c r="G24">
         <v>57.1</v>
@@ -3255,28 +3255,28 @@
         <v>140.4</v>
       </c>
       <c r="M24">
-        <v>3.5212012</v>
+        <v>3.6812558</v>
       </c>
       <c r="N24">
-        <v>136.8787988</v>
+        <v>136.7187442</v>
       </c>
       <c r="O24">
-        <v>47.90757958</v>
+        <v>47.85156047</v>
       </c>
       <c r="P24">
-        <v>88.97121921999999</v>
+        <v>88.86718373000001</v>
       </c>
       <c r="Q24">
-        <v>148.47121922</v>
+        <v>148.36718373</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1299858845635207</v>
+        <v>0.1307558304622176</v>
       </c>
       <c r="T24">
-        <v>1.225007197779774</v>
+        <v>1.236210848756359</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>39.87275705801758</v>
+        <v>38.1391589250603</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1082018394559076</v>
+        <v>0.107821788952269</v>
       </c>
       <c r="C25">
-        <v>257.3075282039163</v>
+        <v>254.8563433014454</v>
       </c>
       <c r="D25">
-        <v>273.3935282039163</v>
+        <v>274.1243433014454</v>
       </c>
       <c r="E25">
-        <v>44.486</v>
+        <v>47.66800000000001</v>
       </c>
       <c r="F25">
-        <v>73.18600000000001</v>
+        <v>76.36800000000001</v>
       </c>
       <c r="G25">
         <v>57.1</v>
@@ -3337,28 +3337,28 @@
         <v>140.4</v>
       </c>
       <c r="M25">
-        <v>3.6812558</v>
+        <v>3.8413104</v>
       </c>
       <c r="N25">
-        <v>136.7187442</v>
+        <v>136.5586896</v>
       </c>
       <c r="O25">
-        <v>47.85156047</v>
+        <v>47.79554136</v>
       </c>
       <c r="P25">
-        <v>88.86718373000001</v>
+        <v>88.76314824000001</v>
       </c>
       <c r="Q25">
-        <v>148.36718373</v>
+        <v>148.26314824</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1307558304622176</v>
+        <v>0.1315460380950907</v>
       </c>
       <c r="T25">
-        <v>1.236210848756359</v>
+        <v>1.24770933265338</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>38.1391589250603</v>
+        <v>36.55002730318279</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.107821788952269</v>
+        <v>0.1074417384486304</v>
       </c>
       <c r="C26">
-        <v>254.8563433014454</v>
+        <v>252.4090759915246</v>
       </c>
       <c r="D26">
-        <v>274.1243433014454</v>
+        <v>274.8590759915245</v>
       </c>
       <c r="E26">
-        <v>47.66799999999999</v>
+        <v>50.84999999999999</v>
       </c>
       <c r="F26">
-        <v>76.36799999999999</v>
+        <v>79.55</v>
       </c>
       <c r="G26">
         <v>57.1</v>
@@ -3419,28 +3419,28 @@
         <v>140.4</v>
       </c>
       <c r="M26">
-        <v>3.841310399999999</v>
+        <v>4.001365</v>
       </c>
       <c r="N26">
-        <v>136.5586896</v>
+        <v>136.398635</v>
       </c>
       <c r="O26">
-        <v>47.79554136</v>
+        <v>47.73952225</v>
       </c>
       <c r="P26">
-        <v>88.76314824000001</v>
+        <v>88.65911275000002</v>
       </c>
       <c r="Q26">
-        <v>148.26314824</v>
+        <v>148.15911275</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1315460380950907</v>
+        <v>0.1323573179315072</v>
       </c>
       <c r="T26">
-        <v>1.24770933265338</v>
+        <v>1.259514442787655</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>36.55002730318279</v>
+        <v>35.08802621105549</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1074417384486304</v>
+        <v>0.1070616879449918</v>
       </c>
       <c r="C27">
-        <v>252.4090759915246</v>
+        <v>249.9657578596627</v>
       </c>
       <c r="D27">
-        <v>274.8590759915245</v>
+        <v>275.5977578596627</v>
       </c>
       <c r="E27">
-        <v>50.84999999999999</v>
+        <v>54.032</v>
       </c>
       <c r="F27">
-        <v>79.55</v>
+        <v>82.732</v>
       </c>
       <c r="G27">
         <v>57.1</v>
@@ -3501,28 +3501,28 @@
         <v>140.4</v>
       </c>
       <c r="M27">
-        <v>4.001365</v>
+        <v>4.161419599999999</v>
       </c>
       <c r="N27">
-        <v>136.398635</v>
+        <v>136.2385804</v>
       </c>
       <c r="O27">
-        <v>47.73952225</v>
+        <v>47.68350314000001</v>
       </c>
       <c r="P27">
-        <v>88.65911275000002</v>
+        <v>88.55507726000002</v>
       </c>
       <c r="Q27">
-        <v>148.15911275</v>
+        <v>148.05507726</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1323573179315072</v>
+        <v>0.1331905242499889</v>
       </c>
       <c r="T27">
-        <v>1.259514442787655</v>
+        <v>1.271638609952586</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>35.08802621105549</v>
+        <v>33.73848674139951</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1070616879449918</v>
+        <v>0.1066816374413532</v>
       </c>
       <c r="C28">
-        <v>249.9657578596627</v>
+        <v>247.5264208318267</v>
       </c>
       <c r="D28">
-        <v>275.5977578596627</v>
+        <v>276.3404208318266</v>
       </c>
       <c r="E28">
-        <v>54.032</v>
+        <v>57.214</v>
       </c>
       <c r="F28">
-        <v>82.732</v>
+        <v>85.914</v>
       </c>
       <c r="G28">
         <v>57.1</v>
@@ -3583,28 +3583,28 @@
         <v>140.4</v>
       </c>
       <c r="M28">
-        <v>4.161419599999999</v>
+        <v>4.3214742</v>
       </c>
       <c r="N28">
-        <v>136.2385804</v>
+        <v>136.0785258</v>
       </c>
       <c r="O28">
-        <v>47.68350314000001</v>
+        <v>47.62748403</v>
       </c>
       <c r="P28">
-        <v>88.55507726000002</v>
+        <v>88.45104176999999</v>
       </c>
       <c r="Q28">
-        <v>148.05507726</v>
+        <v>147.95104177</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1331905242499889</v>
+        <v>0.1340465581388401</v>
       </c>
       <c r="T28">
-        <v>1.271638609952586</v>
+        <v>1.284094946080941</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>33.73848674139951</v>
+        <v>32.4889131583847</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1066816374413532</v>
+        <v>0.1063015869377146</v>
       </c>
       <c r="C29">
-        <v>247.5264208318267</v>
+        <v>245.0910971790416</v>
       </c>
       <c r="D29">
-        <v>276.3404208318266</v>
+        <v>277.0870971790416</v>
       </c>
       <c r="E29">
-        <v>57.214</v>
+        <v>60.396</v>
       </c>
       <c r="F29">
-        <v>85.914</v>
+        <v>89.096</v>
       </c>
       <c r="G29">
         <v>57.1</v>
@@ -3665,28 +3665,28 @@
         <v>140.4</v>
       </c>
       <c r="M29">
-        <v>4.3214742</v>
+        <v>4.4815288</v>
       </c>
       <c r="N29">
-        <v>136.0785258</v>
+        <v>135.9184712</v>
       </c>
       <c r="O29">
-        <v>47.62748403</v>
+        <v>47.57146492</v>
       </c>
       <c r="P29">
-        <v>88.45104176999999</v>
+        <v>88.34700628</v>
       </c>
       <c r="Q29">
-        <v>147.95104177</v>
+        <v>147.84700628</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1340465581388401</v>
+        <v>0.1349263707468259</v>
       </c>
       <c r="T29">
-        <v>1.284094946080941</v>
+        <v>1.296897291546193</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>32.4889131583847</v>
+        <v>31.32859483129954</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1063015869377146</v>
+        <v>0.1059215364340761</v>
       </c>
       <c r="C30">
-        <v>245.0910971790416</v>
+        <v>242.6598195220648</v>
       </c>
       <c r="D30">
-        <v>277.0870971790416</v>
+        <v>277.8378195220648</v>
       </c>
       <c r="E30">
-        <v>60.396</v>
+        <v>63.578</v>
       </c>
       <c r="F30">
-        <v>89.096</v>
+        <v>92.27800000000001</v>
       </c>
       <c r="G30">
         <v>57.1</v>
@@ -3747,28 +3747,28 @@
         <v>140.4</v>
       </c>
       <c r="M30">
-        <v>4.4815288</v>
+        <v>4.6415834</v>
       </c>
       <c r="N30">
-        <v>135.9184712</v>
+        <v>135.7584166</v>
       </c>
       <c r="O30">
-        <v>47.57146492</v>
+        <v>47.51544581</v>
       </c>
       <c r="P30">
-        <v>88.34700628</v>
+        <v>88.24297079000002</v>
       </c>
       <c r="Q30">
-        <v>147.84700628</v>
+        <v>147.74297079</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1349263707468259</v>
+        <v>0.1358309668085578</v>
       </c>
       <c r="T30">
-        <v>1.296897291546193</v>
+        <v>1.310060266461171</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>31.32859483129954</v>
+        <v>30.24829845780645</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1059215364340761</v>
+        <v>0.1055414859304375</v>
       </c>
       <c r="C31">
-        <v>242.6598195220649</v>
+        <v>240.2326208361367</v>
       </c>
       <c r="D31">
-        <v>277.8378195220648</v>
+        <v>278.5926208361366</v>
       </c>
       <c r="E31">
-        <v>63.57799999999999</v>
+        <v>66.75999999999999</v>
       </c>
       <c r="F31">
-        <v>92.27799999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="G31">
         <v>57.1</v>
@@ -3829,28 +3829,28 @@
         <v>140.4</v>
       </c>
       <c r="M31">
-        <v>4.641583399999999</v>
+        <v>4.801638</v>
       </c>
       <c r="N31">
-        <v>135.7584166</v>
+        <v>135.598362</v>
       </c>
       <c r="O31">
-        <v>47.51544581</v>
+        <v>47.4594267</v>
       </c>
       <c r="P31">
-        <v>88.24297079000002</v>
+        <v>88.13893530000001</v>
       </c>
       <c r="Q31">
-        <v>147.74297079</v>
+        <v>147.6389353</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1358309668085578</v>
+        <v>0.1367614084720535</v>
       </c>
       <c r="T31">
-        <v>1.310060266461171</v>
+        <v>1.32359932637372</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>30.24829845780645</v>
+        <v>29.24002184254623</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1055414859304375</v>
+        <v>0.1051614354267989</v>
       </c>
       <c r="C32">
-        <v>240.2326208361367</v>
+        <v>237.8095344558085</v>
       </c>
       <c r="D32">
-        <v>278.5926208361366</v>
+        <v>279.3515344558085</v>
       </c>
       <c r="E32">
-        <v>66.75999999999999</v>
+        <v>69.94199999999999</v>
       </c>
       <c r="F32">
-        <v>95.45999999999999</v>
+        <v>98.642</v>
       </c>
       <c r="G32">
         <v>57.1</v>
@@ -3911,28 +3911,28 @@
         <v>140.4</v>
       </c>
       <c r="M32">
-        <v>4.801638</v>
+        <v>4.961692599999999</v>
       </c>
       <c r="N32">
-        <v>135.598362</v>
+        <v>135.4383074</v>
       </c>
       <c r="O32">
-        <v>47.4594267</v>
+        <v>47.40340759</v>
       </c>
       <c r="P32">
-        <v>88.13893530000001</v>
+        <v>88.03489981000001</v>
       </c>
       <c r="Q32">
-        <v>147.6389353</v>
+        <v>147.53489981</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1367614084720535</v>
+        <v>0.1377188194591288</v>
       </c>
       <c r="T32">
-        <v>1.32359932637372</v>
+        <v>1.337530822805473</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>29.24002184254623</v>
+        <v>28.29679533149636</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1051614354267989</v>
+        <v>0.1047813849231603</v>
       </c>
       <c r="C33">
-        <v>237.8095344558085</v>
+        <v>235.3905940798503</v>
       </c>
       <c r="D33">
-        <v>279.3515344558085</v>
+        <v>280.1145940798503</v>
       </c>
       <c r="E33">
-        <v>69.94199999999999</v>
+        <v>73.124</v>
       </c>
       <c r="F33">
-        <v>98.642</v>
+        <v>101.824</v>
       </c>
       <c r="G33">
         <v>57.1</v>
@@ -3993,28 +3993,28 @@
         <v>140.4</v>
       </c>
       <c r="M33">
-        <v>4.961692599999999</v>
+        <v>5.1217472</v>
       </c>
       <c r="N33">
-        <v>135.4383074</v>
+        <v>135.2782528</v>
       </c>
       <c r="O33">
-        <v>47.40340759</v>
+        <v>47.34738848000001</v>
       </c>
       <c r="P33">
-        <v>88.03489981000001</v>
+        <v>87.93086432000001</v>
       </c>
       <c r="Q33">
-        <v>147.53489981</v>
+        <v>147.43086432</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1377188194591288</v>
+        <v>0.1387043895928828</v>
       </c>
       <c r="T33">
-        <v>1.337530822805473</v>
+        <v>1.351872069132278</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>28.29679533149636</v>
+        <v>27.4125204773871</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1047813849231603</v>
+        <v>0.1044013344195217</v>
       </c>
       <c r="C34">
-        <v>235.3905940798503</v>
+        <v>232.9758337762386</v>
       </c>
       <c r="D34">
-        <v>280.1145940798503</v>
+        <v>280.8818337762386</v>
       </c>
       <c r="E34">
-        <v>73.124</v>
+        <v>76.306</v>
       </c>
       <c r="F34">
-        <v>101.824</v>
+        <v>105.006</v>
       </c>
       <c r="G34">
         <v>57.1</v>
@@ -4075,28 +4075,28 @@
         <v>140.4</v>
       </c>
       <c r="M34">
-        <v>5.1217472</v>
+        <v>5.281801799999999</v>
       </c>
       <c r="N34">
-        <v>135.2782528</v>
+        <v>135.1181982</v>
       </c>
       <c r="O34">
-        <v>47.34738848000001</v>
+        <v>47.29136937</v>
       </c>
       <c r="P34">
-        <v>87.93086432000001</v>
+        <v>87.82682883</v>
       </c>
       <c r="Q34">
-        <v>147.43086432</v>
+        <v>147.32682883</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1387043895928828</v>
+        <v>0.1397193797306295</v>
       </c>
       <c r="T34">
-        <v>1.351872069132278</v>
+        <v>1.36664141236436</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>27.4125204773871</v>
+        <v>26.5818380386784</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1044013344195217</v>
+        <v>0.1040212839158831</v>
       </c>
       <c r="C35">
-        <v>232.9758337762386</v>
+        <v>230.5652879872266</v>
       </c>
       <c r="D35">
-        <v>280.8818337762386</v>
+        <v>281.6532879872265</v>
       </c>
       <c r="E35">
-        <v>76.306</v>
+        <v>79.488</v>
       </c>
       <c r="F35">
-        <v>105.006</v>
+        <v>108.188</v>
       </c>
       <c r="G35">
         <v>57.1</v>
@@ -4157,28 +4157,28 @@
         <v>140.4</v>
       </c>
       <c r="M35">
-        <v>5.281801799999999</v>
+        <v>5.4418564</v>
       </c>
       <c r="N35">
-        <v>135.1181982</v>
+        <v>134.9581436</v>
       </c>
       <c r="O35">
-        <v>47.29136937</v>
+        <v>47.23535026</v>
       </c>
       <c r="P35">
-        <v>87.82682883</v>
+        <v>87.72279334000001</v>
       </c>
       <c r="Q35">
-        <v>147.32682883</v>
+        <v>147.22279334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1397193797306295</v>
+        <v>0.1407651271452775</v>
       </c>
       <c r="T35">
-        <v>1.36664141236436</v>
+        <v>1.381858311451961</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>26.5818380386784</v>
+        <v>25.80001927283491</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1040212839158831</v>
+        <v>0.1036412334122446</v>
       </c>
       <c r="C36">
-        <v>230.5652879872266</v>
+        <v>228.1589915344981</v>
       </c>
       <c r="D36">
-        <v>281.6532879872265</v>
+        <v>282.428991534498</v>
       </c>
       <c r="E36">
-        <v>79.488</v>
+        <v>82.67</v>
       </c>
       <c r="F36">
-        <v>108.188</v>
+        <v>111.37</v>
       </c>
       <c r="G36">
         <v>57.1</v>
@@ -4239,28 +4239,28 @@
         <v>140.4</v>
       </c>
       <c r="M36">
-        <v>5.4418564</v>
+        <v>5.601911</v>
       </c>
       <c r="N36">
-        <v>134.9581436</v>
+        <v>134.798089</v>
       </c>
       <c r="O36">
-        <v>47.23535026</v>
+        <v>47.17933115</v>
       </c>
       <c r="P36">
-        <v>87.72279334000001</v>
+        <v>87.61875785000001</v>
       </c>
       <c r="Q36">
-        <v>147.22279334</v>
+        <v>147.11875785</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1407651271452775</v>
+        <v>0.1418430514034532</v>
       </c>
       <c r="T36">
-        <v>1.381858311451961</v>
+        <v>1.397543422819179</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>25.80001927283491</v>
+        <v>25.06287586503963</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1036412334122446</v>
+        <v>0.103261182908606</v>
       </c>
       <c r="C37">
-        <v>228.1589915344981</v>
+        <v>225.7569796244073</v>
       </c>
       <c r="D37">
-        <v>282.428991534498</v>
+        <v>283.2089796244073</v>
       </c>
       <c r="E37">
-        <v>82.67</v>
+        <v>85.852</v>
       </c>
       <c r="F37">
-        <v>111.37</v>
+        <v>114.552</v>
       </c>
       <c r="G37">
         <v>57.1</v>
@@ -4321,28 +4321,28 @@
         <v>140.4</v>
       </c>
       <c r="M37">
-        <v>5.601911</v>
+        <v>5.7619656</v>
       </c>
       <c r="N37">
-        <v>134.798089</v>
+        <v>134.6380344</v>
       </c>
       <c r="O37">
-        <v>47.17933115</v>
+        <v>47.12331204</v>
       </c>
       <c r="P37">
-        <v>87.61875785000001</v>
+        <v>87.51472236000001</v>
       </c>
       <c r="Q37">
-        <v>147.11875785</v>
+        <v>147.01472236</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1418430514034532</v>
+        <v>0.1429546607946969</v>
       </c>
       <c r="T37">
-        <v>1.397543422819179</v>
+        <v>1.413718693916624</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>25.06287586503963</v>
+        <v>24.36668486878853</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.103261182908606</v>
+        <v>0.1028811324049674</v>
       </c>
       <c r="C38">
-        <v>225.7569796244073</v>
+        <v>223.3592878533049</v>
       </c>
       <c r="D38">
-        <v>283.2089796244073</v>
+        <v>283.9932878533048</v>
       </c>
       <c r="E38">
-        <v>85.85199999999999</v>
+        <v>89.03399999999999</v>
       </c>
       <c r="F38">
-        <v>114.552</v>
+        <v>117.734</v>
       </c>
       <c r="G38">
         <v>57.1</v>
@@ -4403,28 +4403,28 @@
         <v>140.4</v>
       </c>
       <c r="M38">
-        <v>5.761965599999999</v>
+        <v>5.9220202</v>
       </c>
       <c r="N38">
-        <v>134.6380344</v>
+        <v>134.4779798</v>
       </c>
       <c r="O38">
-        <v>47.12331204</v>
+        <v>47.06729293</v>
       </c>
       <c r="P38">
-        <v>87.51472236000001</v>
+        <v>87.41068687000001</v>
       </c>
       <c r="Q38">
-        <v>147.01472236</v>
+        <v>146.91068687</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1429546607946969</v>
+        <v>0.1441015593729641</v>
       </c>
       <c r="T38">
-        <v>1.413718693916624</v>
+        <v>1.430407465683828</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>24.36668486878853</v>
+        <v>23.70812581828073</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1028811324049674</v>
+        <v>0.1025010819013288</v>
       </c>
       <c r="C39">
-        <v>223.3592878533049</v>
+        <v>220.9659522129531</v>
       </c>
       <c r="D39">
-        <v>283.9932878533048</v>
+        <v>284.7819522129531</v>
       </c>
       <c r="E39">
-        <v>89.03399999999999</v>
+        <v>92.21599999999999</v>
       </c>
       <c r="F39">
-        <v>117.734</v>
+        <v>120.916</v>
       </c>
       <c r="G39">
         <v>57.1</v>
@@ -4485,28 +4485,28 @@
         <v>140.4</v>
       </c>
       <c r="M39">
-        <v>5.9220202</v>
+        <v>6.082074799999999</v>
       </c>
       <c r="N39">
-        <v>134.4779798</v>
+        <v>134.3179252</v>
       </c>
       <c r="O39">
-        <v>47.06729293</v>
+        <v>47.01127382000001</v>
       </c>
       <c r="P39">
-        <v>87.41068687000001</v>
+        <v>87.30665138000001</v>
       </c>
       <c r="Q39">
-        <v>146.91068687</v>
+        <v>146.80665138</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1441015593729641</v>
+        <v>0.1452854546795626</v>
       </c>
       <c r="T39">
-        <v>1.430407465683828</v>
+        <v>1.447634584927393</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>23.70812581828073</v>
+        <v>23.08422777043124</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1025010819013288</v>
+        <v>0.1021210313976902</v>
       </c>
       <c r="C40">
-        <v>220.9659522129531</v>
+        <v>218.577009096032</v>
       </c>
       <c r="D40">
-        <v>284.7819522129531</v>
+        <v>285.575009096032</v>
       </c>
       <c r="E40">
-        <v>92.21599999999999</v>
+        <v>95.398</v>
       </c>
       <c r="F40">
-        <v>120.916</v>
+        <v>124.098</v>
       </c>
       <c r="G40">
         <v>57.1</v>
@@ -4567,28 +4567,28 @@
         <v>140.4</v>
       </c>
       <c r="M40">
-        <v>6.082074799999999</v>
+        <v>6.2421294</v>
       </c>
       <c r="N40">
-        <v>134.3179252</v>
+        <v>134.1578706</v>
       </c>
       <c r="O40">
-        <v>47.01127382000001</v>
+        <v>46.95525471</v>
       </c>
       <c r="P40">
-        <v>87.30665138000001</v>
+        <v>87.20261589</v>
       </c>
       <c r="Q40">
-        <v>146.80665138</v>
+        <v>146.70261589</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1452854546795626</v>
+        <v>0.1465081662257217</v>
       </c>
       <c r="T40">
-        <v>1.447634584927393</v>
+        <v>1.465426527752716</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>23.08422777043124</v>
+        <v>22.49232449426633</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1021210313976902</v>
+        <v>0.1017409808940517</v>
       </c>
       <c r="C41">
-        <v>218.577009096032</v>
+        <v>216.1924953017369</v>
       </c>
       <c r="D41">
-        <v>285.575009096032</v>
+        <v>286.3724953017369</v>
       </c>
       <c r="E41">
-        <v>95.398</v>
+        <v>98.58</v>
       </c>
       <c r="F41">
-        <v>124.098</v>
+        <v>127.28</v>
       </c>
       <c r="G41">
         <v>57.1</v>
@@ -4649,28 +4649,28 @@
         <v>140.4</v>
       </c>
       <c r="M41">
-        <v>6.2421294</v>
+        <v>6.402184</v>
       </c>
       <c r="N41">
-        <v>134.1578706</v>
+        <v>133.997816</v>
       </c>
       <c r="O41">
-        <v>46.95525471</v>
+        <v>46.8992356</v>
       </c>
       <c r="P41">
-        <v>87.20261589</v>
+        <v>87.0985804</v>
       </c>
       <c r="Q41">
-        <v>146.70261589</v>
+        <v>146.5985804</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1465081662257217</v>
+        <v>0.1477716348234194</v>
       </c>
       <c r="T41">
-        <v>1.465426527752716</v>
+        <v>1.483811535338882</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>22.49232449426633</v>
+        <v>21.93001638190967</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1017409808940517</v>
+        <v>0.1013609303904131</v>
       </c>
       <c r="C42">
-        <v>216.1924953017369</v>
+        <v>213.8124480414704</v>
       </c>
       <c r="D42">
-        <v>286.3724953017369</v>
+        <v>287.1744480414704</v>
       </c>
       <c r="E42">
-        <v>98.58</v>
+        <v>101.762</v>
       </c>
       <c r="F42">
-        <v>127.28</v>
+        <v>130.462</v>
       </c>
       <c r="G42">
         <v>57.1</v>
@@ -4731,28 +4731,28 @@
         <v>140.4</v>
       </c>
       <c r="M42">
-        <v>6.402184</v>
+        <v>6.562238600000001</v>
       </c>
       <c r="N42">
-        <v>133.997816</v>
+        <v>133.8377614</v>
       </c>
       <c r="O42">
-        <v>46.8992356</v>
+        <v>46.84321649</v>
       </c>
       <c r="P42">
-        <v>87.0985804</v>
+        <v>86.99454491</v>
       </c>
       <c r="Q42">
-        <v>146.5985804</v>
+        <v>146.49454491</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1477716348234194</v>
+        <v>0.1490779328651069</v>
       </c>
       <c r="T42">
-        <v>1.483811535338882</v>
+        <v>1.502819763521189</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>21.93001638190967</v>
+        <v>21.39513793357041</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1013609303904131</v>
+        <v>0.1009808798867745</v>
       </c>
       <c r="C43">
-        <v>213.8124480414704</v>
+        <v>211.4369049446304</v>
       </c>
       <c r="D43">
-        <v>287.1744480414704</v>
+        <v>287.9809049446304</v>
       </c>
       <c r="E43">
-        <v>101.762</v>
+        <v>104.944</v>
       </c>
       <c r="F43">
-        <v>130.462</v>
+        <v>133.644</v>
       </c>
       <c r="G43">
         <v>57.1</v>
@@ -4813,28 +4813,28 @@
         <v>140.4</v>
       </c>
       <c r="M43">
-        <v>6.562238600000001</v>
+        <v>6.7222932</v>
       </c>
       <c r="N43">
-        <v>133.8377614</v>
+        <v>133.6777068</v>
       </c>
       <c r="O43">
-        <v>46.84321649</v>
+        <v>46.78719738</v>
       </c>
       <c r="P43">
-        <v>86.99454491</v>
+        <v>86.89050942</v>
       </c>
       <c r="Q43">
-        <v>146.49454491</v>
+        <v>146.39050942</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1490779328651069</v>
+        <v>0.1504292756668526</v>
       </c>
       <c r="T43">
-        <v>1.502819763521189</v>
+        <v>1.522483447847714</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>21.39513793357041</v>
+        <v>20.88572988753302</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1009808798867745</v>
+        <v>0.1006008293831359</v>
       </c>
       <c r="C44">
-        <v>211.4369049446305</v>
+        <v>209.0659040644962</v>
       </c>
       <c r="D44">
-        <v>287.9809049446304</v>
+        <v>288.7919040644962</v>
       </c>
       <c r="E44">
-        <v>104.944</v>
+        <v>108.126</v>
       </c>
       <c r="F44">
-        <v>133.644</v>
+        <v>136.826</v>
       </c>
       <c r="G44">
         <v>57.1</v>
@@ -4895,28 +4895,28 @@
         <v>140.4</v>
       </c>
       <c r="M44">
-        <v>6.722293199999998</v>
+        <v>6.882347799999999</v>
       </c>
       <c r="N44">
-        <v>133.6777068</v>
+        <v>133.5176522</v>
       </c>
       <c r="O44">
-        <v>46.78719738</v>
+        <v>46.73117827</v>
       </c>
       <c r="P44">
-        <v>86.89050942</v>
+        <v>86.78647393000001</v>
       </c>
       <c r="Q44">
-        <v>146.39050942</v>
+        <v>146.28647393</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1504292756668526</v>
+        <v>0.1518280340055016</v>
       </c>
       <c r="T44">
-        <v>1.522483447847714</v>
+        <v>1.542837086010257</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>20.88572988753303</v>
+        <v>20.40001523898575</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1006008293831359</v>
+        <v>0.1002207788794973</v>
       </c>
       <c r="C45">
-        <v>209.0659040644962</v>
+        <v>206.699483884213</v>
       </c>
       <c r="D45">
-        <v>288.7919040644962</v>
+        <v>289.607483884213</v>
       </c>
       <c r="E45">
-        <v>108.126</v>
+        <v>111.308</v>
       </c>
       <c r="F45">
-        <v>136.826</v>
+        <v>140.008</v>
       </c>
       <c r="G45">
         <v>57.1</v>
@@ -4977,28 +4977,28 @@
         <v>140.4</v>
       </c>
       <c r="M45">
-        <v>6.882347799999999</v>
+        <v>7.0424024</v>
       </c>
       <c r="N45">
-        <v>133.5176522</v>
+        <v>133.3575976</v>
       </c>
       <c r="O45">
-        <v>46.73117827</v>
+        <v>46.67515916000001</v>
       </c>
       <c r="P45">
-        <v>86.78647393000001</v>
+        <v>86.68243844000001</v>
       </c>
       <c r="Q45">
-        <v>146.28647393</v>
+        <v>146.18243844</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1518280340055016</v>
+        <v>0.1532767479991024</v>
       </c>
       <c r="T45">
-        <v>1.542837086010257</v>
+        <v>1.563917639821462</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>20.40001523898575</v>
+        <v>19.9363785290088</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1002207788794973</v>
+        <v>0.09984072837585875</v>
       </c>
       <c r="C46">
-        <v>206.699483884213</v>
+        <v>204.3376833228799</v>
       </c>
       <c r="D46">
-        <v>289.607483884213</v>
+        <v>290.4276833228799</v>
       </c>
       <c r="E46">
-        <v>111.308</v>
+        <v>114.49</v>
       </c>
       <c r="F46">
-        <v>140.008</v>
+        <v>143.19</v>
       </c>
       <c r="G46">
         <v>57.1</v>
@@ -5059,28 +5059,28 @@
         <v>140.4</v>
       </c>
       <c r="M46">
-        <v>7.0424024</v>
+        <v>7.202457</v>
       </c>
       <c r="N46">
-        <v>133.3575976</v>
+        <v>133.197543</v>
       </c>
       <c r="O46">
-        <v>46.67515916000001</v>
+        <v>46.61914005</v>
       </c>
       <c r="P46">
-        <v>86.68243844000001</v>
+        <v>86.57840295</v>
       </c>
       <c r="Q46">
-        <v>146.18243844</v>
+        <v>146.07840295</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1532767479991024</v>
+        <v>0.1547781425015614</v>
       </c>
       <c r="T46">
-        <v>1.563917639821462</v>
+        <v>1.585764759225803</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>19.9363785290088</v>
+        <v>19.49334789503082</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09984072837585875</v>
+        <v>0.09946067787222018</v>
       </c>
       <c r="C47">
-        <v>204.3376833228799</v>
+        <v>201.9805417417404</v>
       </c>
       <c r="D47">
-        <v>290.4276833228799</v>
+        <v>291.2525417417403</v>
       </c>
       <c r="E47">
-        <v>114.49</v>
+        <v>117.672</v>
       </c>
       <c r="F47">
-        <v>143.19</v>
+        <v>146.372</v>
       </c>
       <c r="G47">
         <v>57.1</v>
@@ -5141,28 +5141,28 @@
         <v>140.4</v>
       </c>
       <c r="M47">
-        <v>7.202457</v>
+        <v>7.3625116</v>
       </c>
       <c r="N47">
-        <v>133.197543</v>
+        <v>133.0374884</v>
       </c>
       <c r="O47">
-        <v>46.61914005</v>
+        <v>46.56312094</v>
       </c>
       <c r="P47">
-        <v>86.57840295</v>
+        <v>86.47436746</v>
       </c>
       <c r="Q47">
-        <v>146.07840295</v>
+        <v>145.97436746</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1547781425015614</v>
+        <v>0.1563351442078151</v>
       </c>
       <c r="T47">
-        <v>1.585764759225803</v>
+        <v>1.608421031200674</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>19.49334789503082</v>
+        <v>19.06957946253015</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09946067787222018</v>
+        <v>0.09908062736858159</v>
       </c>
       <c r="C48">
-        <v>201.9805417417404</v>
+        <v>199.628098950479</v>
       </c>
       <c r="D48">
-        <v>291.2525417417403</v>
+        <v>292.082098950479</v>
       </c>
       <c r="E48">
-        <v>117.672</v>
+        <v>120.854</v>
       </c>
       <c r="F48">
-        <v>146.372</v>
+        <v>149.554</v>
       </c>
       <c r="G48">
         <v>57.1</v>
@@ -5223,28 +5223,28 @@
         <v>140.4</v>
       </c>
       <c r="M48">
-        <v>7.3625116</v>
+        <v>7.5225662</v>
       </c>
       <c r="N48">
-        <v>133.0374884</v>
+        <v>132.8774338</v>
       </c>
       <c r="O48">
-        <v>46.56312094</v>
+        <v>46.50710183</v>
       </c>
       <c r="P48">
-        <v>86.47436746</v>
+        <v>86.37033197000001</v>
       </c>
       <c r="Q48">
-        <v>145.97436746</v>
+        <v>145.87033197</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1563351442078151</v>
+        <v>0.157950900695437</v>
       </c>
       <c r="T48">
-        <v>1.608421031200674</v>
+        <v>1.631932256834975</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>19.06957946253015</v>
+        <v>18.66384372928483</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09908062736858159</v>
+        <v>0.09870057686494302</v>
       </c>
       <c r="C49">
-        <v>199.628098950479</v>
+        <v>197.2803952136258</v>
       </c>
       <c r="D49">
-        <v>292.082098950479</v>
+        <v>292.9163952136258</v>
       </c>
       <c r="E49">
-        <v>120.854</v>
+        <v>124.036</v>
       </c>
       <c r="F49">
-        <v>149.554</v>
+        <v>152.736</v>
       </c>
       <c r="G49">
         <v>57.1</v>
@@ -5305,28 +5305,28 @@
         <v>140.4</v>
       </c>
       <c r="M49">
-        <v>7.5225662</v>
+        <v>7.6826208</v>
       </c>
       <c r="N49">
-        <v>132.8774338</v>
+        <v>132.7173792</v>
       </c>
       <c r="O49">
-        <v>46.50710183</v>
+        <v>46.45108272</v>
       </c>
       <c r="P49">
-        <v>86.37033197000001</v>
+        <v>86.26629648000001</v>
       </c>
       <c r="Q49">
-        <v>145.87033197</v>
+        <v>145.76629648</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.157950900695437</v>
+        <v>0.1596288016633519</v>
       </c>
       <c r="T49">
-        <v>1.631932256834975</v>
+        <v>1.656347760378287</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>18.66384372928483</v>
+        <v>18.27501365159139</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09870057686494302</v>
+        <v>0.09832052636130442</v>
       </c>
       <c r="C50">
-        <v>197.2803952136259</v>
+        <v>194.9374712570718</v>
       </c>
       <c r="D50">
-        <v>292.9163952136258</v>
+        <v>293.7554712570718</v>
       </c>
       <c r="E50">
-        <v>124.036</v>
+        <v>127.218</v>
       </c>
       <c r="F50">
-        <v>152.736</v>
+        <v>155.918</v>
       </c>
       <c r="G50">
         <v>57.1</v>
@@ -5387,28 +5387,28 @@
         <v>140.4</v>
       </c>
       <c r="M50">
-        <v>7.682620799999999</v>
+        <v>7.842675399999998</v>
       </c>
       <c r="N50">
-        <v>132.7173792</v>
+        <v>132.5573246</v>
       </c>
       <c r="O50">
-        <v>46.45108272</v>
+        <v>46.39506361</v>
       </c>
       <c r="P50">
-        <v>86.26629648000001</v>
+        <v>86.16226099000002</v>
       </c>
       <c r="Q50">
-        <v>145.76629648</v>
+        <v>145.66226099</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1596288016633519</v>
+        <v>0.1613725026692243</v>
       </c>
       <c r="T50">
-        <v>1.656347760378287</v>
+        <v>1.681720734648787</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>18.2750136515914</v>
+        <v>17.90205418931403</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09832052636130442</v>
+        <v>0.09794047585766584</v>
       </c>
       <c r="C51">
-        <v>194.9374712570718</v>
+        <v>192.5993682746946</v>
       </c>
       <c r="D51">
-        <v>293.7554712570718</v>
+        <v>294.5993682746946</v>
       </c>
       <c r="E51">
-        <v>127.218</v>
+        <v>130.4</v>
       </c>
       <c r="F51">
-        <v>155.918</v>
+        <v>159.1</v>
       </c>
       <c r="G51">
         <v>57.1</v>
@@ -5469,28 +5469,28 @@
         <v>140.4</v>
       </c>
       <c r="M51">
-        <v>7.842675399999998</v>
+        <v>8.00273</v>
       </c>
       <c r="N51">
-        <v>132.5573246</v>
+        <v>132.39727</v>
       </c>
       <c r="O51">
-        <v>46.39506361</v>
+        <v>46.33904449999999</v>
       </c>
       <c r="P51">
-        <v>86.16226099000002</v>
+        <v>86.05822549999999</v>
       </c>
       <c r="Q51">
-        <v>145.66226099</v>
+        <v>145.5582255</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1613725026692243</v>
+        <v>0.1631859517153317</v>
       </c>
       <c r="T51">
-        <v>1.681720734648787</v>
+        <v>1.708108627890108</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>17.90205418931403</v>
+        <v>17.54401310552774</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09794047585766584</v>
+        <v>0.09756042535402726</v>
       </c>
       <c r="C52">
-        <v>192.5993682746946</v>
+        <v>190.2661279351009</v>
       </c>
       <c r="D52">
-        <v>294.5993682746946</v>
+        <v>295.4481279351009</v>
       </c>
       <c r="E52">
-        <v>130.4</v>
+        <v>133.582</v>
       </c>
       <c r="F52">
-        <v>159.1</v>
+        <v>162.282</v>
       </c>
       <c r="G52">
         <v>57.1</v>
@@ -5551,28 +5551,28 @@
         <v>140.4</v>
       </c>
       <c r="M52">
-        <v>8.00273</v>
+        <v>8.1627846</v>
       </c>
       <c r="N52">
-        <v>132.39727</v>
+        <v>132.2372154</v>
       </c>
       <c r="O52">
-        <v>46.33904449999999</v>
+        <v>46.28302539</v>
       </c>
       <c r="P52">
-        <v>86.05822549999999</v>
+        <v>85.95419000999999</v>
       </c>
       <c r="Q52">
-        <v>145.5582255</v>
+        <v>145.45419001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1631859517153317</v>
+        <v>0.1650734190898515</v>
       </c>
       <c r="T52">
-        <v>1.708108627890108</v>
+        <v>1.735573577998421</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>17.54401310552774</v>
+        <v>17.20001284855661</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09756042535402726</v>
+        <v>0.09718037485038868</v>
       </c>
       <c r="C53">
-        <v>190.2661279351009</v>
+        <v>187.9377923884848</v>
       </c>
       <c r="D53">
-        <v>295.4481279351009</v>
+        <v>296.3017923884848</v>
       </c>
       <c r="E53">
-        <v>133.582</v>
+        <v>136.764</v>
       </c>
       <c r="F53">
-        <v>162.282</v>
+        <v>165.464</v>
       </c>
       <c r="G53">
         <v>57.1</v>
@@ -5633,28 +5633,28 @@
         <v>140.4</v>
       </c>
       <c r="M53">
-        <v>8.1627846</v>
+        <v>8.322839199999999</v>
       </c>
       <c r="N53">
-        <v>132.2372154</v>
+        <v>132.0771608</v>
       </c>
       <c r="O53">
-        <v>46.28302539</v>
+        <v>46.22700628</v>
       </c>
       <c r="P53">
-        <v>85.95419000999999</v>
+        <v>85.85015452</v>
       </c>
       <c r="Q53">
-        <v>145.45419001</v>
+        <v>145.35015452</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1650734190898515</v>
+        <v>0.1670395309383098</v>
       </c>
       <c r="T53">
-        <v>1.735573577998421</v>
+        <v>1.764182901027915</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>17.20001284855661</v>
+        <v>16.86924337069975</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09718037485038868</v>
+        <v>0.09680032434675009</v>
       </c>
       <c r="C54">
-        <v>187.9377923884848</v>
+        <v>185.6144042736049</v>
       </c>
       <c r="D54">
-        <v>296.3017923884848</v>
+        <v>297.1604042736049</v>
       </c>
       <c r="E54">
-        <v>136.764</v>
+        <v>139.946</v>
       </c>
       <c r="F54">
-        <v>165.464</v>
+        <v>168.646</v>
       </c>
       <c r="G54">
         <v>57.1</v>
@@ -5715,28 +5715,28 @@
         <v>140.4</v>
       </c>
       <c r="M54">
-        <v>8.322839199999999</v>
+        <v>8.482893800000001</v>
       </c>
       <c r="N54">
-        <v>132.0771608</v>
+        <v>131.9171062</v>
       </c>
       <c r="O54">
-        <v>46.22700628</v>
+        <v>46.17098717</v>
       </c>
       <c r="P54">
-        <v>85.85015452</v>
+        <v>85.74611903000002</v>
       </c>
       <c r="Q54">
-        <v>145.35015452</v>
+        <v>145.24611903</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1670395309383098</v>
+        <v>0.1690893071207449</v>
       </c>
       <c r="T54">
-        <v>1.764182901027915</v>
+        <v>1.794009642058663</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>16.86924337069975</v>
+        <v>16.55095575993183</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09680032434675009</v>
+        <v>0.09642027384311151</v>
       </c>
       <c r="C55">
-        <v>185.6144042736049</v>
+        <v>183.296006724884</v>
       </c>
       <c r="D55">
-        <v>297.1604042736049</v>
+        <v>298.024006724884</v>
       </c>
       <c r="E55">
-        <v>139.946</v>
+        <v>143.128</v>
       </c>
       <c r="F55">
-        <v>168.646</v>
+        <v>171.828</v>
       </c>
       <c r="G55">
         <v>57.1</v>
@@ -5797,28 +5797,28 @@
         <v>140.4</v>
       </c>
       <c r="M55">
-        <v>8.482893800000001</v>
+        <v>8.6429484</v>
       </c>
       <c r="N55">
-        <v>131.9171062</v>
+        <v>131.7570516</v>
       </c>
       <c r="O55">
-        <v>46.17098717</v>
+        <v>46.11496806</v>
       </c>
       <c r="P55">
-        <v>85.74611903000002</v>
+        <v>85.64208354000002</v>
       </c>
       <c r="Q55">
-        <v>145.24611903</v>
+        <v>145.14208354</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1690893071207449</v>
+        <v>0.1712282040067642</v>
       </c>
       <c r="T55">
-        <v>1.794009642058663</v>
+        <v>1.825133197916835</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>16.55095575993183</v>
+        <v>16.24445657919235</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09642027384311151</v>
+        <v>0.09604022333947293</v>
       </c>
       <c r="C56">
-        <v>183.296006724884</v>
+        <v>180.9826433796325</v>
       </c>
       <c r="D56">
-        <v>298.024006724884</v>
+        <v>298.8926433796325</v>
       </c>
       <c r="E56">
-        <v>143.128</v>
+        <v>146.31</v>
       </c>
       <c r="F56">
-        <v>171.828</v>
+        <v>175.01</v>
       </c>
       <c r="G56">
         <v>57.1</v>
@@ -5879,28 +5879,28 @@
         <v>140.4</v>
       </c>
       <c r="M56">
-        <v>8.6429484</v>
+        <v>8.803003</v>
       </c>
       <c r="N56">
-        <v>131.7570516</v>
+        <v>131.596997</v>
       </c>
       <c r="O56">
-        <v>46.11496806</v>
+        <v>46.05894895</v>
       </c>
       <c r="P56">
-        <v>85.64208354000002</v>
+        <v>85.53804805000001</v>
       </c>
       <c r="Q56">
-        <v>145.14208354</v>
+        <v>145.03804805</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1712282040067642</v>
+        <v>0.1734621629766065</v>
       </c>
       <c r="T56">
-        <v>1.825133197916835</v>
+        <v>1.857640022924259</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>16.24445657919235</v>
+        <v>15.94910282320704</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09604022333947293</v>
+        <v>0.09566017283583433</v>
       </c>
       <c r="C57">
-        <v>180.9826433796325</v>
+        <v>178.6743583853985</v>
       </c>
       <c r="D57">
-        <v>298.8926433796325</v>
+        <v>299.7663583853985</v>
       </c>
       <c r="E57">
-        <v>146.31</v>
+        <v>149.492</v>
       </c>
       <c r="F57">
-        <v>175.01</v>
+        <v>178.192</v>
       </c>
       <c r="G57">
         <v>57.1</v>
@@ -5961,28 +5961,28 @@
         <v>140.4</v>
       </c>
       <c r="M57">
-        <v>8.803003</v>
+        <v>8.963057599999999</v>
       </c>
       <c r="N57">
-        <v>131.596997</v>
+        <v>131.4369424</v>
       </c>
       <c r="O57">
-        <v>46.05894895</v>
+        <v>46.00292984000001</v>
       </c>
       <c r="P57">
-        <v>85.53804805000001</v>
+        <v>85.43401256000001</v>
       </c>
       <c r="Q57">
-        <v>145.03804805</v>
+        <v>144.93401256</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1734621629766065</v>
+        <v>0.1757976655359872</v>
       </c>
       <c r="T57">
-        <v>1.857640022924259</v>
+        <v>1.891624430886566</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>15.94910282320704</v>
+        <v>15.66429741564977</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09566017283583433</v>
+        <v>0.09528012233219575</v>
       </c>
       <c r="C58">
-        <v>178.6743583853985</v>
+        <v>176.3711964074471</v>
       </c>
       <c r="D58">
-        <v>299.7663583853985</v>
+        <v>300.6451964074471</v>
       </c>
       <c r="E58">
-        <v>149.492</v>
+        <v>152.674</v>
       </c>
       <c r="F58">
-        <v>178.192</v>
+        <v>181.374</v>
       </c>
       <c r="G58">
         <v>57.1</v>
@@ -6043,28 +6043,28 @@
         <v>140.4</v>
       </c>
       <c r="M58">
-        <v>8.963057599999999</v>
+        <v>9.123112200000001</v>
       </c>
       <c r="N58">
-        <v>131.4369424</v>
+        <v>131.2768878</v>
       </c>
       <c r="O58">
-        <v>46.00292984000001</v>
+        <v>45.94691073</v>
       </c>
       <c r="P58">
-        <v>85.43401256000001</v>
+        <v>85.32997707</v>
       </c>
       <c r="Q58">
-        <v>144.93401256</v>
+        <v>144.82997707</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1757976655359872</v>
+        <v>0.1782417961213855</v>
       </c>
       <c r="T58">
-        <v>1.891624430886566</v>
+        <v>1.927189508986655</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>15.66429741564977</v>
+        <v>15.38948518028749</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09528012233219575</v>
+        <v>0.09490007182855717</v>
       </c>
       <c r="C59">
-        <v>176.3711964074471</v>
+        <v>174.0732026363721</v>
       </c>
       <c r="D59">
-        <v>300.6451964074471</v>
+        <v>301.5292026363721</v>
       </c>
       <c r="E59">
-        <v>152.674</v>
+        <v>155.856</v>
       </c>
       <c r="F59">
-        <v>181.374</v>
+        <v>184.556</v>
       </c>
       <c r="G59">
         <v>57.1</v>
@@ -6125,28 +6125,28 @@
         <v>140.4</v>
       </c>
       <c r="M59">
-        <v>9.123112200000001</v>
+        <v>9.2831668</v>
       </c>
       <c r="N59">
-        <v>131.2768878</v>
+        <v>131.1168332</v>
       </c>
       <c r="O59">
-        <v>45.94691073</v>
+        <v>45.89089162</v>
       </c>
       <c r="P59">
-        <v>85.32997707</v>
+        <v>85.22594158000001</v>
       </c>
       <c r="Q59">
-        <v>144.82997707</v>
+        <v>144.72594158</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1782417961213855</v>
+        <v>0.1808023138775171</v>
       </c>
       <c r="T59">
-        <v>1.927189508986655</v>
+        <v>1.964448162234367</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>15.38948518028749</v>
+        <v>15.12414922890322</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09490007182855718</v>
+        <v>0.0945200213249186</v>
       </c>
       <c r="C60">
-        <v>174.0732026363722</v>
+        <v>171.7804227958418</v>
       </c>
       <c r="D60">
-        <v>301.5292026363721</v>
+        <v>302.4184227958417</v>
       </c>
       <c r="E60">
-        <v>155.856</v>
+        <v>159.038</v>
       </c>
       <c r="F60">
-        <v>184.556</v>
+        <v>187.738</v>
       </c>
       <c r="G60">
         <v>57.1</v>
@@ -6207,28 +6207,28 @@
         <v>140.4</v>
       </c>
       <c r="M60">
-        <v>9.283166799999998</v>
+        <v>9.443221399999999</v>
       </c>
       <c r="N60">
-        <v>131.1168332</v>
+        <v>130.9567786</v>
       </c>
       <c r="O60">
-        <v>45.89089162</v>
+        <v>45.83487251</v>
       </c>
       <c r="P60">
-        <v>85.22594158000001</v>
+        <v>85.12190609000001</v>
       </c>
       <c r="Q60">
-        <v>144.72594158</v>
+        <v>144.62190609</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1808023138775171</v>
+        <v>0.1834877349388258</v>
       </c>
       <c r="T60">
-        <v>1.964448162234366</v>
+        <v>2.003524310762455</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>15.12414922890323</v>
+        <v>14.86780771654893</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0945200213249186</v>
+        <v>0.09413997082128002</v>
       </c>
       <c r="C61">
-        <v>171.7804227958418</v>
+        <v>169.4929031504823</v>
       </c>
       <c r="D61">
-        <v>302.4184227958417</v>
+        <v>303.3129031504823</v>
       </c>
       <c r="E61">
-        <v>159.038</v>
+        <v>162.22</v>
       </c>
       <c r="F61">
-        <v>187.738</v>
+        <v>190.92</v>
       </c>
       <c r="G61">
         <v>57.1</v>
@@ -6289,28 +6289,28 @@
         <v>140.4</v>
       </c>
       <c r="M61">
-        <v>9.443221399999999</v>
+        <v>9.603275999999999</v>
       </c>
       <c r="N61">
-        <v>130.9567786</v>
+        <v>130.796724</v>
       </c>
       <c r="O61">
-        <v>45.83487251</v>
+        <v>45.7788534</v>
       </c>
       <c r="P61">
-        <v>85.12190609000001</v>
+        <v>85.01787060000001</v>
       </c>
       <c r="Q61">
-        <v>144.62190609</v>
+        <v>144.5178706</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1834877349388258</v>
+        <v>0.1863074270532001</v>
       </c>
       <c r="T61">
-        <v>2.003524310762455</v>
+        <v>2.044554266716947</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>14.86780771654893</v>
+        <v>14.62001092127312</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09413997082128002</v>
+        <v>0.09375992031764144</v>
       </c>
       <c r="C62">
-        <v>169.4929031504823</v>
+        <v>167.210690513902</v>
       </c>
       <c r="D62">
-        <v>303.3129031504823</v>
+        <v>304.212690513902</v>
       </c>
       <c r="E62">
-        <v>162.22</v>
+        <v>165.402</v>
       </c>
       <c r="F62">
-        <v>190.92</v>
+        <v>194.102</v>
       </c>
       <c r="G62">
         <v>57.1</v>
@@ -6371,28 +6371,28 @@
         <v>140.4</v>
       </c>
       <c r="M62">
-        <v>9.603275999999999</v>
+        <v>9.763330599999998</v>
       </c>
       <c r="N62">
-        <v>130.796724</v>
+        <v>130.6366694</v>
       </c>
       <c r="O62">
-        <v>45.7788534</v>
+        <v>45.72283429</v>
       </c>
       <c r="P62">
-        <v>85.01787060000001</v>
+        <v>84.91383511000001</v>
       </c>
       <c r="Q62">
-        <v>144.5178706</v>
+        <v>144.41383511</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1863074270532001</v>
+        <v>0.1892717187631832</v>
       </c>
       <c r="T62">
-        <v>2.044554266716947</v>
+        <v>2.087688322976799</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>14.62001092127312</v>
+        <v>14.38033861108831</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09375992031764144</v>
+        <v>0.09337986981400287</v>
       </c>
       <c r="C63">
-        <v>167.210690513902</v>
+        <v>164.9338322568582</v>
       </c>
       <c r="D63">
-        <v>304.212690513902</v>
+        <v>305.1178322568582</v>
       </c>
       <c r="E63">
-        <v>165.402</v>
+        <v>168.584</v>
       </c>
       <c r="F63">
-        <v>194.102</v>
+        <v>197.284</v>
       </c>
       <c r="G63">
         <v>57.1</v>
@@ -6453,28 +6453,28 @@
         <v>140.4</v>
       </c>
       <c r="M63">
-        <v>9.763330599999998</v>
+        <v>9.923385199999998</v>
       </c>
       <c r="N63">
-        <v>130.6366694</v>
+        <v>130.4766148</v>
       </c>
       <c r="O63">
-        <v>45.72283429</v>
+        <v>45.66681517999999</v>
       </c>
       <c r="P63">
-        <v>84.91383511000001</v>
+        <v>84.80979962000001</v>
       </c>
       <c r="Q63">
-        <v>144.41383511</v>
+        <v>144.30979962</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1892717187631832</v>
+        <v>0.1923920258263233</v>
       </c>
       <c r="T63">
-        <v>2.087688322976799</v>
+        <v>2.133092592724011</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>14.38033861108831</v>
+        <v>14.14839766574818</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09337986981400287</v>
+        <v>0.09299981931036426</v>
       </c>
       <c r="C64">
-        <v>164.9338322568582</v>
+        <v>162.6623763155707</v>
       </c>
       <c r="D64">
-        <v>305.1178322568582</v>
+        <v>306.0283763155707</v>
       </c>
       <c r="E64">
-        <v>168.584</v>
+        <v>171.766</v>
       </c>
       <c r="F64">
-        <v>197.284</v>
+        <v>200.466</v>
       </c>
       <c r="G64">
         <v>57.1</v>
@@ -6535,28 +6535,28 @@
         <v>140.4</v>
       </c>
       <c r="M64">
-        <v>9.923385199999998</v>
+        <v>10.0834398</v>
       </c>
       <c r="N64">
-        <v>130.4766148</v>
+        <v>130.3165602</v>
       </c>
       <c r="O64">
-        <v>45.66681517999999</v>
+        <v>45.61079607</v>
       </c>
       <c r="P64">
-        <v>84.80979962000001</v>
+        <v>84.70576413000001</v>
       </c>
       <c r="Q64">
-        <v>144.30979962</v>
+        <v>144.20576413</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1923920258263233</v>
+        <v>0.1956809981361196</v>
       </c>
       <c r="T64">
-        <v>2.133092592724011</v>
+        <v>2.180951147322423</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>14.14839766574818</v>
+        <v>13.92381992502201</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09299981931036426</v>
+        <v>0.09261976880672571</v>
       </c>
       <c r="C65">
-        <v>162.6623763155707</v>
+        <v>160.3963712001838</v>
       </c>
       <c r="D65">
-        <v>306.0283763155707</v>
+        <v>306.9443712001838</v>
       </c>
       <c r="E65">
-        <v>171.766</v>
+        <v>174.948</v>
       </c>
       <c r="F65">
-        <v>200.466</v>
+        <v>203.648</v>
       </c>
       <c r="G65">
         <v>57.1</v>
@@ -6617,28 +6617,28 @@
         <v>140.4</v>
       </c>
       <c r="M65">
-        <v>10.0834398</v>
+        <v>10.2434944</v>
       </c>
       <c r="N65">
-        <v>130.3165602</v>
+        <v>130.1565056</v>
       </c>
       <c r="O65">
-        <v>45.61079607</v>
+        <v>45.55477696</v>
       </c>
       <c r="P65">
-        <v>84.70576413000001</v>
+        <v>84.60172864</v>
       </c>
       <c r="Q65">
-        <v>144.20576413</v>
+        <v>144.10172864</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1956809981361196</v>
+        <v>0.1991526911297936</v>
       </c>
       <c r="T65">
-        <v>2.180951147322423</v>
+        <v>2.231468510509636</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>13.92381992502201</v>
+        <v>13.70626023869355</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09261976880672571</v>
+        <v>0.09223971830308711</v>
       </c>
       <c r="C66">
-        <v>160.3963712001838</v>
+        <v>158.1358660033824</v>
       </c>
       <c r="D66">
-        <v>306.9443712001838</v>
+        <v>307.8658660033824</v>
       </c>
       <c r="E66">
-        <v>174.948</v>
+        <v>178.13</v>
       </c>
       <c r="F66">
-        <v>203.648</v>
+        <v>206.83</v>
       </c>
       <c r="G66">
         <v>57.1</v>
@@ -6699,28 +6699,28 @@
         <v>140.4</v>
       </c>
       <c r="M66">
-        <v>10.2434944</v>
+        <v>10.403549</v>
       </c>
       <c r="N66">
-        <v>130.1565056</v>
+        <v>129.996451</v>
       </c>
       <c r="O66">
-        <v>45.55477696</v>
+        <v>45.49875785</v>
       </c>
       <c r="P66">
-        <v>84.60172864</v>
+        <v>84.49769315</v>
       </c>
       <c r="Q66">
-        <v>144.10172864</v>
+        <v>143.99769315</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1991526911297936</v>
+        <v>0.2028227665802489</v>
       </c>
       <c r="T66">
-        <v>2.231468510509636</v>
+        <v>2.28487258016469</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>13.70626023869355</v>
+        <v>13.4953946965598</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09223971830308711</v>
+        <v>0.09185966779944851</v>
       </c>
       <c r="C67">
-        <v>158.1358660033824</v>
+        <v>155.8809104091619</v>
       </c>
       <c r="D67">
-        <v>307.8658660033824</v>
+        <v>308.7929104091618</v>
       </c>
       <c r="E67">
-        <v>178.13</v>
+        <v>181.312</v>
       </c>
       <c r="F67">
-        <v>206.83</v>
+        <v>210.012</v>
       </c>
       <c r="G67">
         <v>57.1</v>
@@ -6781,28 +6781,28 @@
         <v>140.4</v>
       </c>
       <c r="M67">
-        <v>10.403549</v>
+        <v>10.5636036</v>
       </c>
       <c r="N67">
-        <v>129.996451</v>
+        <v>129.8363964</v>
       </c>
       <c r="O67">
-        <v>45.49875785</v>
+        <v>45.44273874</v>
       </c>
       <c r="P67">
-        <v>84.49769315</v>
+        <v>84.39365766</v>
       </c>
       <c r="Q67">
-        <v>143.99769315</v>
+        <v>143.89365766</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2028227665802489</v>
+        <v>0.2067087288219074</v>
       </c>
       <c r="T67">
-        <v>2.28487258016469</v>
+        <v>2.341418065681806</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>13.4953946965598</v>
+        <v>13.2909190193392</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09185966779944851</v>
+        <v>0.09147961729580995</v>
       </c>
       <c r="C68">
-        <v>155.8809104091619</v>
+        <v>153.6315547017579</v>
       </c>
       <c r="D68">
-        <v>308.7929104091618</v>
+        <v>309.7255547017579</v>
       </c>
       <c r="E68">
-        <v>181.312</v>
+        <v>184.494</v>
       </c>
       <c r="F68">
-        <v>210.012</v>
+        <v>213.194</v>
       </c>
       <c r="G68">
         <v>57.1</v>
@@ -6863,28 +6863,28 @@
         <v>140.4</v>
       </c>
       <c r="M68">
-        <v>10.5636036</v>
+        <v>10.7236582</v>
       </c>
       <c r="N68">
-        <v>129.8363964</v>
+        <v>129.6763418</v>
       </c>
       <c r="O68">
-        <v>45.44273874</v>
+        <v>45.38671963</v>
       </c>
       <c r="P68">
-        <v>84.39365766</v>
+        <v>84.28962217000002</v>
       </c>
       <c r="Q68">
-        <v>143.89365766</v>
+        <v>143.78962217</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2067087288219074</v>
+        <v>0.2108302039266968</v>
       </c>
       <c r="T68">
-        <v>2.341418065681806</v>
+        <v>2.401390550321171</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>13.2909190193392</v>
+        <v>13.09254709367742</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09147961729580995</v>
+        <v>0.09109956679217136</v>
       </c>
       <c r="C69">
-        <v>153.6315547017579</v>
+        <v>151.3878497747387</v>
       </c>
       <c r="D69">
-        <v>309.7255547017579</v>
+        <v>310.6638497747387</v>
       </c>
       <c r="E69">
-        <v>184.494</v>
+        <v>187.676</v>
       </c>
       <c r="F69">
-        <v>213.194</v>
+        <v>216.376</v>
       </c>
       <c r="G69">
         <v>57.1</v>
@@ -6945,28 +6945,28 @@
         <v>140.4</v>
       </c>
       <c r="M69">
-        <v>10.7236582</v>
+        <v>10.8837128</v>
       </c>
       <c r="N69">
-        <v>129.6763418</v>
+        <v>129.5162872</v>
       </c>
       <c r="O69">
-        <v>45.38671963</v>
+        <v>45.33070051999999</v>
       </c>
       <c r="P69">
-        <v>84.28962217000002</v>
+        <v>84.18558668</v>
       </c>
       <c r="Q69">
-        <v>143.78962217</v>
+        <v>143.68558668</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2108302039266968</v>
+        <v>0.2152092712255355</v>
       </c>
       <c r="T69">
-        <v>2.401390550321171</v>
+        <v>2.465111315250497</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>13.09254709367742</v>
+        <v>12.90000963641745</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09109956679217136</v>
+        <v>0.09139226628853278</v>
       </c>
       <c r="C70">
-        <v>151.3878497747387</v>
+        <v>147.4827109416811</v>
       </c>
       <c r="D70">
-        <v>310.6638497747387</v>
+        <v>309.9407109416811</v>
       </c>
       <c r="E70">
-        <v>187.676</v>
+        <v>190.858</v>
       </c>
       <c r="F70">
-        <v>216.376</v>
+        <v>219.558</v>
       </c>
       <c r="G70">
         <v>57.1</v>
@@ -7027,45 +7027,45 @@
         <v>140.4</v>
       </c>
       <c r="M70">
-        <v>10.8837128</v>
+        <v>11.3731044</v>
       </c>
       <c r="N70">
-        <v>129.5162872</v>
+        <v>129.0268956</v>
       </c>
       <c r="O70">
-        <v>45.33070051999999</v>
+        <v>45.15941346</v>
       </c>
       <c r="P70">
-        <v>84.18558668</v>
+        <v>83.86748214000002</v>
       </c>
       <c r="Q70">
-        <v>143.68558668</v>
+        <v>143.36748214</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2152092712255355</v>
+        <v>0.2198708589952671</v>
       </c>
       <c r="T70">
-        <v>2.465111315250497</v>
+        <v>2.532943097272037</v>
       </c>
       <c r="U70">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V70">
         <v>0.35</v>
       </c>
       <c r="W70">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y70">
-        <v>12.90000963641745</v>
+        <v>12.34491437535736</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09139226628853278</v>
+        <v>0.09102196578489419</v>
       </c>
       <c r="C71">
-        <v>147.4827109416811</v>
+        <v>145.2161358728255</v>
       </c>
       <c r="D71">
-        <v>309.9407109416811</v>
+        <v>310.8561358728255</v>
       </c>
       <c r="E71">
-        <v>190.858</v>
+        <v>194.04</v>
       </c>
       <c r="F71">
-        <v>219.558</v>
+        <v>222.74</v>
       </c>
       <c r="G71">
         <v>57.1</v>
@@ -7109,28 +7109,28 @@
         <v>140.4</v>
       </c>
       <c r="M71">
-        <v>11.3731044</v>
+        <v>11.537932</v>
       </c>
       <c r="N71">
-        <v>129.0268956</v>
+        <v>128.862068</v>
       </c>
       <c r="O71">
-        <v>45.15941346</v>
+        <v>45.10172379999999</v>
       </c>
       <c r="P71">
-        <v>83.86748214000002</v>
+        <v>83.76034419999999</v>
       </c>
       <c r="Q71">
-        <v>143.36748214</v>
+        <v>143.2603442</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2198708589952671</v>
+        <v>0.2248432192829806</v>
       </c>
       <c r="T71">
-        <v>2.532943097272037</v>
+        <v>2.605296998095013</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>12.34491437535736</v>
+        <v>12.16855845570939</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09102196578489419</v>
+        <v>0.09065166528125561</v>
       </c>
       <c r="C72">
-        <v>145.2161358728255</v>
+        <v>142.9549843265261</v>
       </c>
       <c r="D72">
-        <v>310.8561358728255</v>
+        <v>311.7769843265261</v>
       </c>
       <c r="E72">
-        <v>194.04</v>
+        <v>197.222</v>
       </c>
       <c r="F72">
-        <v>222.74</v>
+        <v>225.922</v>
       </c>
       <c r="G72">
         <v>57.1</v>
@@ -7191,28 +7191,28 @@
         <v>140.4</v>
       </c>
       <c r="M72">
-        <v>11.537932</v>
+        <v>11.7027596</v>
       </c>
       <c r="N72">
-        <v>128.862068</v>
+        <v>128.6972404</v>
       </c>
       <c r="O72">
-        <v>45.10172379999999</v>
+        <v>45.04403413999999</v>
       </c>
       <c r="P72">
-        <v>83.76034419999999</v>
+        <v>83.65320626</v>
       </c>
       <c r="Q72">
-        <v>143.2603442</v>
+        <v>143.15320626</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2248432192829806</v>
+        <v>0.230158500969847</v>
       </c>
       <c r="T72">
-        <v>2.605296998095013</v>
+        <v>2.682640823112678</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>12.16855845570939</v>
+        <v>11.99717030844588</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09065166528125561</v>
+        <v>0.09028136477761703</v>
       </c>
       <c r="C73">
-        <v>142.9549843265261</v>
+        <v>140.6993046442519</v>
       </c>
       <c r="D73">
-        <v>311.7769843265261</v>
+        <v>312.7033046442519</v>
       </c>
       <c r="E73">
-        <v>197.222</v>
+        <v>200.404</v>
       </c>
       <c r="F73">
-        <v>225.922</v>
+        <v>229.104</v>
       </c>
       <c r="G73">
         <v>57.1</v>
@@ -7273,28 +7273,28 @@
         <v>140.4</v>
       </c>
       <c r="M73">
-        <v>11.7027596</v>
+        <v>11.8675872</v>
       </c>
       <c r="N73">
-        <v>128.6972404</v>
+        <v>128.5324128</v>
       </c>
       <c r="O73">
-        <v>45.04403413999999</v>
+        <v>44.98634448</v>
       </c>
       <c r="P73">
-        <v>83.65320626</v>
+        <v>83.54606832</v>
       </c>
       <c r="Q73">
-        <v>143.15320626</v>
+        <v>143.04606832</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2301585009698469</v>
+        <v>0.2358534456343465</v>
       </c>
       <c r="T73">
-        <v>2.682640823112677</v>
+        <v>2.765509207060175</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>11.99717030844588</v>
+        <v>11.8305429430508</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09028136477761703</v>
+        <v>0.08991106427397844</v>
       </c>
       <c r="C74">
-        <v>140.6993046442519</v>
+        <v>138.4491457436932</v>
       </c>
       <c r="D74">
-        <v>312.7033046442519</v>
+        <v>313.6351457436931</v>
       </c>
       <c r="E74">
-        <v>200.404</v>
+        <v>203.586</v>
       </c>
       <c r="F74">
-        <v>229.104</v>
+        <v>232.286</v>
       </c>
       <c r="G74">
         <v>57.1</v>
@@ -7355,28 +7355,28 @@
         <v>140.4</v>
       </c>
       <c r="M74">
-        <v>11.8675872</v>
+        <v>12.0324148</v>
       </c>
       <c r="N74">
-        <v>128.5324128</v>
+        <v>128.3675852</v>
       </c>
       <c r="O74">
-        <v>44.98634448</v>
+        <v>44.92865482</v>
       </c>
       <c r="P74">
-        <v>83.54606832</v>
+        <v>83.43893038000002</v>
       </c>
       <c r="Q74">
-        <v>143.04606832</v>
+        <v>142.93893038</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2358534456343465</v>
+        <v>0.241970238051772</v>
       </c>
       <c r="T74">
-        <v>2.765509207060175</v>
+        <v>2.854515989818597</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>11.8305429430508</v>
+        <v>11.66848071095422</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08991106427397844</v>
+        <v>0.08954076377033986</v>
       </c>
       <c r="C75">
-        <v>138.4491457436932</v>
+        <v>136.2045571273722</v>
       </c>
       <c r="D75">
-        <v>313.6351457436931</v>
+        <v>314.5725571273721</v>
       </c>
       <c r="E75">
-        <v>203.586</v>
+        <v>206.768</v>
       </c>
       <c r="F75">
-        <v>232.286</v>
+        <v>235.468</v>
       </c>
       <c r="G75">
         <v>57.1</v>
@@ -7437,28 +7437,28 @@
         <v>140.4</v>
       </c>
       <c r="M75">
-        <v>12.0324148</v>
+        <v>12.1972424</v>
       </c>
       <c r="N75">
-        <v>128.3675852</v>
+        <v>128.2027576</v>
       </c>
       <c r="O75">
-        <v>44.92865482</v>
+        <v>44.87096516</v>
       </c>
       <c r="P75">
-        <v>83.43893038000002</v>
+        <v>83.33179244000002</v>
       </c>
       <c r="Q75">
-        <v>142.93893038</v>
+        <v>142.83179244</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.241970238051772</v>
+        <v>0.2485575529628456</v>
       </c>
       <c r="T75">
-        <v>2.854515989818597</v>
+        <v>2.950369448173822</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>11.66848071095422</v>
+        <v>11.51079853918456</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08954076377033986</v>
+        <v>0.08917046326670128</v>
       </c>
       <c r="C76">
-        <v>136.2045571273722</v>
+        <v>133.9655888914103</v>
       </c>
       <c r="D76">
-        <v>314.5725571273721</v>
+        <v>315.5155888914102</v>
       </c>
       <c r="E76">
-        <v>206.768</v>
+        <v>209.95</v>
       </c>
       <c r="F76">
-        <v>235.468</v>
+        <v>238.65</v>
       </c>
       <c r="G76">
         <v>57.1</v>
@@ -7519,28 +7519,28 @@
         <v>140.4</v>
       </c>
       <c r="M76">
-        <v>12.1972424</v>
+        <v>12.36207</v>
       </c>
       <c r="N76">
-        <v>128.2027576</v>
+        <v>128.03793</v>
       </c>
       <c r="O76">
-        <v>44.87096516</v>
+        <v>44.8132755</v>
       </c>
       <c r="P76">
-        <v>83.33179244000002</v>
+        <v>83.22465450000001</v>
       </c>
       <c r="Q76">
-        <v>142.83179244</v>
+        <v>142.7246545</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2485575529628456</v>
+        <v>0.2556718530668051</v>
       </c>
       <c r="T76">
-        <v>2.950369448173822</v>
+        <v>3.053891183197466</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>11.51079853918456</v>
+        <v>11.35732122532877</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08917046326670128</v>
+        <v>0.08880016276306268</v>
       </c>
       <c r="C77">
-        <v>133.9655888914103</v>
+        <v>131.7322917344513</v>
       </c>
       <c r="D77">
-        <v>315.5155888914102</v>
+        <v>316.4642917344513</v>
       </c>
       <c r="E77">
-        <v>209.95</v>
+        <v>213.132</v>
       </c>
       <c r="F77">
-        <v>238.65</v>
+        <v>241.832</v>
       </c>
       <c r="G77">
         <v>57.1</v>
@@ -7601,28 +7601,28 @@
         <v>140.4</v>
       </c>
       <c r="M77">
-        <v>12.36207</v>
+        <v>12.5268976</v>
       </c>
       <c r="N77">
-        <v>128.03793</v>
+        <v>127.8731024</v>
       </c>
       <c r="O77">
-        <v>44.8132755</v>
+        <v>44.75558584</v>
       </c>
       <c r="P77">
-        <v>83.22465450000001</v>
+        <v>83.11751656000001</v>
       </c>
       <c r="Q77">
-        <v>142.7246545</v>
+        <v>142.61751656</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2556718530668051</v>
+        <v>0.2633790115127612</v>
       </c>
       <c r="T77">
-        <v>3.053891183197466</v>
+        <v>3.166039729473079</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>11.35732122532877</v>
+        <v>11.20788278815339</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08880016276306268</v>
+        <v>0.08842986225942411</v>
       </c>
       <c r="C78">
-        <v>131.7322917344513</v>
+        <v>129.5047169667475</v>
       </c>
       <c r="D78">
-        <v>316.4642917344513</v>
+        <v>317.4187169667475</v>
       </c>
       <c r="E78">
-        <v>213.132</v>
+        <v>216.314</v>
       </c>
       <c r="F78">
-        <v>241.832</v>
+        <v>245.014</v>
       </c>
       <c r="G78">
         <v>57.1</v>
@@ -7683,28 +7683,28 @@
         <v>140.4</v>
       </c>
       <c r="M78">
-        <v>12.5268976</v>
+        <v>12.6917252</v>
       </c>
       <c r="N78">
-        <v>127.8731024</v>
+        <v>127.7082748</v>
       </c>
       <c r="O78">
-        <v>44.75558584</v>
+        <v>44.69789617999999</v>
       </c>
       <c r="P78">
-        <v>83.11751656000001</v>
+        <v>83.01037862000001</v>
       </c>
       <c r="Q78">
-        <v>142.61751656</v>
+        <v>142.51037862</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2633790115127612</v>
+        <v>0.27175635764967</v>
       </c>
       <c r="T78">
-        <v>3.166039729473079</v>
+        <v>3.287940323250919</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>11.20788278815339</v>
+        <v>11.06232586882672</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08842986225942411</v>
+        <v>0.08805956175578553</v>
       </c>
       <c r="C79">
-        <v>129.5047169667475</v>
+        <v>127.2829165194105</v>
       </c>
       <c r="D79">
-        <v>317.4187169667475</v>
+        <v>318.3789165194105</v>
       </c>
       <c r="E79">
-        <v>216.314</v>
+        <v>219.496</v>
       </c>
       <c r="F79">
-        <v>245.014</v>
+        <v>248.196</v>
       </c>
       <c r="G79">
         <v>57.1</v>
@@ -7765,28 +7765,28 @@
         <v>140.4</v>
       </c>
       <c r="M79">
-        <v>12.6917252</v>
+        <v>12.8565528</v>
       </c>
       <c r="N79">
-        <v>127.7082748</v>
+        <v>127.5434472</v>
       </c>
       <c r="O79">
-        <v>44.69789617999999</v>
+        <v>44.64020652</v>
       </c>
       <c r="P79">
-        <v>83.01037862000001</v>
+        <v>82.90324068000001</v>
       </c>
       <c r="Q79">
-        <v>142.51037862</v>
+        <v>142.40324068</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.27175635764967</v>
+        <v>0.280895280708116</v>
       </c>
       <c r="T79">
-        <v>3.287940323250919</v>
+        <v>3.420922789190382</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>11.06232586882672</v>
+        <v>10.92050117820074</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08805956175578553</v>
+        <v>0.08768926125214695</v>
       </c>
       <c r="C80">
-        <v>127.2829165194105</v>
+        <v>125.0669429538303</v>
       </c>
       <c r="D80">
-        <v>318.3789165194105</v>
+        <v>319.3449429538303</v>
       </c>
       <c r="E80">
-        <v>219.496</v>
+        <v>222.678</v>
       </c>
       <c r="F80">
-        <v>248.196</v>
+        <v>251.378</v>
       </c>
       <c r="G80">
         <v>57.1</v>
@@ -7847,28 +7847,28 @@
         <v>140.4</v>
       </c>
       <c r="M80">
-        <v>12.8565528</v>
+        <v>13.0213804</v>
       </c>
       <c r="N80">
-        <v>127.5434472</v>
+        <v>127.3786196</v>
       </c>
       <c r="O80">
-        <v>44.64020652</v>
+        <v>44.58251686</v>
       </c>
       <c r="P80">
-        <v>82.90324068000001</v>
+        <v>82.79610274000001</v>
       </c>
       <c r="Q80">
-        <v>142.40324068</v>
+        <v>142.29610274</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.280895280708116</v>
+        <v>0.290904577391176</v>
       </c>
       <c r="T80">
-        <v>3.420922789190382</v>
+        <v>3.566570251885984</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>10.92050117820074</v>
+        <v>10.78226698607162</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08768926125214695</v>
+        <v>0.08731896074850837</v>
       </c>
       <c r="C81">
-        <v>125.0669429538303</v>
+        <v>122.8568494712659</v>
       </c>
       <c r="D81">
-        <v>319.3449429538303</v>
+        <v>320.3168494712659</v>
       </c>
       <c r="E81">
-        <v>222.678</v>
+        <v>225.86</v>
       </c>
       <c r="F81">
-        <v>251.378</v>
+        <v>254.56</v>
       </c>
       <c r="G81">
         <v>57.1</v>
@@ -7929,28 +7929,28 @@
         <v>140.4</v>
       </c>
       <c r="M81">
-        <v>13.0213804</v>
+        <v>13.186208</v>
       </c>
       <c r="N81">
-        <v>127.3786196</v>
+        <v>127.213792</v>
       </c>
       <c r="O81">
-        <v>44.58251686</v>
+        <v>44.5248272</v>
       </c>
       <c r="P81">
-        <v>82.79610274000001</v>
+        <v>82.68896480000001</v>
       </c>
       <c r="Q81">
-        <v>142.29610274</v>
+        <v>142.1889648</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.290904577391176</v>
+        <v>0.3019148037425419</v>
       </c>
       <c r="T81">
-        <v>3.566570251885984</v>
+        <v>3.726782460851145</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>10.78226698607162</v>
+        <v>10.64748864874572</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08731896074850837</v>
+        <v>0.08694866024486979</v>
       </c>
       <c r="C82">
-        <v>122.8568494712659</v>
+        <v>120.6526899226125</v>
       </c>
       <c r="D82">
-        <v>320.3168494712659</v>
+        <v>321.2946899226125</v>
       </c>
       <c r="E82">
-        <v>225.86</v>
+        <v>229.042</v>
       </c>
       <c r="F82">
-        <v>254.56</v>
+        <v>257.742</v>
       </c>
       <c r="G82">
         <v>57.1</v>
@@ -8011,28 +8011,28 @@
         <v>140.4</v>
       </c>
       <c r="M82">
-        <v>13.186208</v>
+        <v>13.3510356</v>
       </c>
       <c r="N82">
-        <v>127.213792</v>
+        <v>127.0489644</v>
       </c>
       <c r="O82">
-        <v>44.5248272</v>
+        <v>44.46713754</v>
       </c>
       <c r="P82">
-        <v>82.68896480000001</v>
+        <v>82.58182686000001</v>
       </c>
       <c r="Q82">
-        <v>142.1889648</v>
+        <v>142.08182686</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3019148037425419</v>
+        <v>0.3140840012887884</v>
       </c>
       <c r="T82">
-        <v>3.726782460851145</v>
+        <v>3.903859112865272</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>10.64748864874572</v>
+        <v>10.51603817160071</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08694866024486979</v>
+        <v>0.0865783597412312</v>
       </c>
       <c r="C83">
-        <v>120.6526899226125</v>
+        <v>118.4545188183476</v>
       </c>
       <c r="D83">
-        <v>321.2946899226125</v>
+        <v>322.2785188183476</v>
       </c>
       <c r="E83">
-        <v>229.042</v>
+        <v>232.224</v>
       </c>
       <c r="F83">
-        <v>257.742</v>
+        <v>260.924</v>
       </c>
       <c r="G83">
         <v>57.1</v>
@@ -8093,28 +8093,28 @@
         <v>140.4</v>
       </c>
       <c r="M83">
-        <v>13.3510356</v>
+        <v>13.5158632</v>
       </c>
       <c r="N83">
-        <v>127.0489644</v>
+        <v>126.8841368</v>
       </c>
       <c r="O83">
-        <v>44.46713754</v>
+        <v>44.40944788</v>
       </c>
       <c r="P83">
-        <v>82.58182686000001</v>
+        <v>82.47468892000001</v>
       </c>
       <c r="Q83">
-        <v>142.08182686</v>
+        <v>141.97468892</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3140840012887884</v>
+        <v>0.327605331895729</v>
       </c>
       <c r="T83">
-        <v>3.903859112865272</v>
+        <v>4.100610948436523</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>10.51603817160071</v>
+        <v>10.38779380365436</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0865783597412312</v>
+        <v>0.08620805923759262</v>
       </c>
       <c r="C84">
-        <v>118.4545188183476</v>
+        <v>116.2623913386603</v>
       </c>
       <c r="D84">
-        <v>322.2785188183476</v>
+        <v>323.2683913386603</v>
       </c>
       <c r="E84">
-        <v>232.224</v>
+        <v>235.406</v>
       </c>
       <c r="F84">
-        <v>260.924</v>
+        <v>264.106</v>
       </c>
       <c r="G84">
         <v>57.1</v>
@@ -8175,28 +8175,28 @@
         <v>140.4</v>
       </c>
       <c r="M84">
-        <v>13.5158632</v>
+        <v>13.6806908</v>
       </c>
       <c r="N84">
-        <v>126.8841368</v>
+        <v>126.7193092</v>
       </c>
       <c r="O84">
-        <v>44.40944788</v>
+        <v>44.35175822</v>
       </c>
       <c r="P84">
-        <v>82.47468892000001</v>
+        <v>82.36755098</v>
       </c>
       <c r="Q84">
-        <v>141.97468892</v>
+        <v>141.86755098</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.327605331895729</v>
+        <v>0.3427174072799568</v>
       </c>
       <c r="T84">
-        <v>4.100610948436523</v>
+        <v>4.320510058780863</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>10.38779380365436</v>
+        <v>10.26263966144166</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08620805923759262</v>
+        <v>0.08583775873395402</v>
       </c>
       <c r="C85">
-        <v>116.2623913386603</v>
+        <v>114.0763633437682</v>
       </c>
       <c r="D85">
-        <v>323.2683913386603</v>
+        <v>324.2643633437681</v>
       </c>
       <c r="E85">
-        <v>235.406</v>
+        <v>238.588</v>
       </c>
       <c r="F85">
-        <v>264.106</v>
+        <v>267.288</v>
       </c>
       <c r="G85">
         <v>57.1</v>
@@ -8257,28 +8257,28 @@
         <v>140.4</v>
       </c>
       <c r="M85">
-        <v>13.6806908</v>
+        <v>13.8455184</v>
       </c>
       <c r="N85">
-        <v>126.7193092</v>
+        <v>126.5544816</v>
       </c>
       <c r="O85">
-        <v>44.35175822</v>
+        <v>44.29406856</v>
       </c>
       <c r="P85">
-        <v>82.36755098</v>
+        <v>82.26041304</v>
       </c>
       <c r="Q85">
-        <v>141.86755098</v>
+        <v>141.76041304</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3427174072799568</v>
+        <v>0.3597184920872128</v>
       </c>
       <c r="T85">
-        <v>4.320510058780863</v>
+        <v>4.567896557918245</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>10.26263966144166</v>
+        <v>10.14046537975783</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08583775873395404</v>
+        <v>0.08546745823031546</v>
       </c>
       <c r="C86">
-        <v>114.0763633437682</v>
+        <v>111.896491384425</v>
       </c>
       <c r="D86">
-        <v>324.2643633437681</v>
+        <v>325.266491384425</v>
       </c>
       <c r="E86">
-        <v>238.588</v>
+        <v>241.77</v>
       </c>
       <c r="F86">
-        <v>267.288</v>
+        <v>270.47</v>
       </c>
       <c r="G86">
         <v>57.1</v>
@@ -8339,28 +8339,28 @@
         <v>140.4</v>
       </c>
       <c r="M86">
-        <v>13.8455184</v>
+        <v>14.010346</v>
       </c>
       <c r="N86">
-        <v>126.5544816</v>
+        <v>126.389654</v>
       </c>
       <c r="O86">
-        <v>44.29406856</v>
+        <v>44.2363789</v>
       </c>
       <c r="P86">
-        <v>82.26041304</v>
+        <v>82.1532751</v>
       </c>
       <c r="Q86">
-        <v>141.76041304</v>
+        <v>141.6532751</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3597184920872127</v>
+        <v>0.378986388202103</v>
       </c>
       <c r="T86">
-        <v>4.567896557918242</v>
+        <v>4.848267923607276</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>10.14046537975783</v>
+        <v>10.0211657870548</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08546745823031546</v>
+        <v>0.08509715772667688</v>
       </c>
       <c r="C87">
-        <v>111.896491384425</v>
+        <v>109.7228327126249</v>
       </c>
       <c r="D87">
-        <v>325.266491384425</v>
+        <v>326.2748327126249</v>
       </c>
       <c r="E87">
-        <v>241.77</v>
+        <v>244.952</v>
       </c>
       <c r="F87">
-        <v>270.47</v>
+        <v>273.652</v>
       </c>
       <c r="G87">
         <v>57.1</v>
@@ -8421,28 +8421,28 @@
         <v>140.4</v>
       </c>
       <c r="M87">
-        <v>14.010346</v>
+        <v>14.1751736</v>
       </c>
       <c r="N87">
-        <v>126.389654</v>
+        <v>126.2248264</v>
       </c>
       <c r="O87">
-        <v>44.2363789</v>
+        <v>44.17868924</v>
       </c>
       <c r="P87">
-        <v>82.1532751</v>
+        <v>82.04613716</v>
       </c>
       <c r="Q87">
-        <v>141.6532751</v>
+        <v>141.54613716</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.378986388202103</v>
+        <v>0.4010068409048348</v>
       </c>
       <c r="T87">
-        <v>4.848267923607276</v>
+        <v>5.168692341537599</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>10.0211657870548</v>
+        <v>9.904640603484392</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08509715772667688</v>
+        <v>0.08568820722303828</v>
       </c>
       <c r="C88">
-        <v>109.7228327126249</v>
+        <v>104.9343437831689</v>
       </c>
       <c r="D88">
-        <v>326.2748327126249</v>
+        <v>324.6683437831689</v>
       </c>
       <c r="E88">
-        <v>244.952</v>
+        <v>248.134</v>
       </c>
       <c r="F88">
-        <v>273.652</v>
+        <v>276.834</v>
       </c>
       <c r="G88">
         <v>57.1</v>
@@ -8503,45 +8503,45 @@
         <v>140.4</v>
       </c>
       <c r="M88">
-        <v>14.1751736</v>
+        <v>14.810619</v>
       </c>
       <c r="N88">
-        <v>126.2248264</v>
+        <v>125.589381</v>
       </c>
       <c r="O88">
-        <v>44.17868924</v>
+        <v>43.95628335</v>
       </c>
       <c r="P88">
-        <v>82.04613716</v>
+        <v>81.63309765</v>
       </c>
       <c r="Q88">
-        <v>141.54613716</v>
+        <v>141.13309765</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4010068409048348</v>
+        <v>0.426415055561833</v>
       </c>
       <c r="T88">
-        <v>5.168692341537599</v>
+        <v>5.538412823764895</v>
       </c>
       <c r="U88">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V88">
         <v>0.35</v>
       </c>
       <c r="W88">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>9.904640603484392</v>
+        <v>9.479684812633423</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08568820722303828</v>
+        <v>0.0853289567193997</v>
       </c>
       <c r="C89">
-        <v>104.9343437831689</v>
+        <v>102.7269054308442</v>
       </c>
       <c r="D89">
-        <v>324.6683437831689</v>
+        <v>325.6429054308442</v>
       </c>
       <c r="E89">
-        <v>248.134</v>
+        <v>251.316</v>
       </c>
       <c r="F89">
-        <v>276.834</v>
+        <v>280.016</v>
       </c>
       <c r="G89">
         <v>57.1</v>
@@ -8585,28 +8585,28 @@
         <v>140.4</v>
       </c>
       <c r="M89">
-        <v>14.810619</v>
+        <v>14.980856</v>
       </c>
       <c r="N89">
-        <v>125.589381</v>
+        <v>125.419144</v>
       </c>
       <c r="O89">
-        <v>43.95628335</v>
+        <v>43.8967004</v>
       </c>
       <c r="P89">
-        <v>81.63309765</v>
+        <v>81.5224436</v>
       </c>
       <c r="Q89">
-        <v>141.13309765</v>
+        <v>141.0224436</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.426415055561833</v>
+        <v>0.4560579726616643</v>
       </c>
       <c r="T89">
-        <v>5.538412823764895</v>
+        <v>5.969753386363408</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>9.479684812633423</v>
+        <v>9.371961121580769</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0853289567193997</v>
+        <v>0.08496970621576112</v>
       </c>
       <c r="C90">
-        <v>102.7269054308442</v>
+        <v>100.5253354050525</v>
       </c>
       <c r="D90">
-        <v>325.6429054308442</v>
+        <v>326.6233354050524</v>
       </c>
       <c r="E90">
-        <v>251.316</v>
+        <v>254.498</v>
       </c>
       <c r="F90">
-        <v>280.016</v>
+        <v>283.198</v>
       </c>
       <c r="G90">
         <v>57.1</v>
@@ -8667,28 +8667,28 @@
         <v>140.4</v>
       </c>
       <c r="M90">
-        <v>14.980856</v>
+        <v>15.151093</v>
       </c>
       <c r="N90">
-        <v>125.419144</v>
+        <v>125.248907</v>
       </c>
       <c r="O90">
-        <v>43.8967004</v>
+        <v>43.83711745</v>
       </c>
       <c r="P90">
-        <v>81.5224436</v>
+        <v>81.41178955000001</v>
       </c>
       <c r="Q90">
-        <v>141.0224436</v>
+        <v>140.91178955</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4560579726616643</v>
+        <v>0.4910905110523739</v>
       </c>
       <c r="T90">
-        <v>5.969753386363408</v>
+        <v>6.479519505798013</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>9.371961121580769</v>
+        <v>9.266658187630425</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08496970621576112</v>
+        <v>0.08461045571212254</v>
       </c>
       <c r="C91">
-        <v>100.5253354050525</v>
+        <v>98.32968687008264</v>
       </c>
       <c r="D91">
-        <v>326.6233354050524</v>
+        <v>327.6096868700826</v>
       </c>
       <c r="E91">
-        <v>254.498</v>
+        <v>257.68</v>
       </c>
       <c r="F91">
-        <v>283.198</v>
+        <v>286.38</v>
       </c>
       <c r="G91">
         <v>57.1</v>
@@ -8749,28 +8749,28 @@
         <v>140.4</v>
       </c>
       <c r="M91">
-        <v>15.151093</v>
+        <v>15.32133</v>
       </c>
       <c r="N91">
-        <v>125.248907</v>
+        <v>125.07867</v>
       </c>
       <c r="O91">
-        <v>43.83711745</v>
+        <v>43.7775345</v>
       </c>
       <c r="P91">
-        <v>81.41178955000001</v>
+        <v>81.3011355</v>
       </c>
       <c r="Q91">
-        <v>140.91178955</v>
+        <v>140.8011355</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4910905110523739</v>
+        <v>0.5331295571212256</v>
       </c>
       <c r="T91">
-        <v>6.479519505798013</v>
+        <v>7.091238849119541</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>9.266658187630425</v>
+        <v>9.163695318878975</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08461045571212254</v>
+        <v>0.08425120520848395</v>
       </c>
       <c r="C92">
-        <v>98.32968687008264</v>
+        <v>96.14001363436046</v>
       </c>
       <c r="D92">
-        <v>327.6096868700826</v>
+        <v>328.6020136343604</v>
       </c>
       <c r="E92">
-        <v>257.68</v>
+        <v>260.862</v>
       </c>
       <c r="F92">
-        <v>286.38</v>
+        <v>289.562</v>
       </c>
       <c r="G92">
         <v>57.1</v>
@@ -8831,28 +8831,28 @@
         <v>140.4</v>
       </c>
       <c r="M92">
-        <v>15.32133</v>
+        <v>15.491567</v>
       </c>
       <c r="N92">
-        <v>125.07867</v>
+        <v>124.908433</v>
       </c>
       <c r="O92">
-        <v>43.7775345</v>
+        <v>43.71795155</v>
       </c>
       <c r="P92">
-        <v>81.3011355</v>
+        <v>81.19048145000001</v>
       </c>
       <c r="Q92">
-        <v>140.8011355</v>
+        <v>140.69048145</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5331295571212256</v>
+        <v>0.5845106134275997</v>
       </c>
       <c r="T92">
-        <v>7.091238849119541</v>
+        <v>7.838895824290296</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>9.163695318878975</v>
+        <v>9.062995370319864</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08425120520848395</v>
+        <v>0.08389195470484537</v>
       </c>
       <c r="C93">
-        <v>96.14001363436046</v>
+        <v>93.95637016023312</v>
       </c>
       <c r="D93">
-        <v>328.6020136343604</v>
+        <v>329.6003701602331</v>
       </c>
       <c r="E93">
-        <v>260.862</v>
+        <v>264.044</v>
       </c>
       <c r="F93">
-        <v>289.562</v>
+        <v>292.744</v>
       </c>
       <c r="G93">
         <v>57.1</v>
@@ -8913,28 +8913,28 @@
         <v>140.4</v>
       </c>
       <c r="M93">
-        <v>15.491567</v>
+        <v>15.661804</v>
       </c>
       <c r="N93">
-        <v>124.908433</v>
+        <v>124.738196</v>
       </c>
       <c r="O93">
-        <v>43.71795155</v>
+        <v>43.6583686</v>
       </c>
       <c r="P93">
-        <v>81.19048145000001</v>
+        <v>81.0798274</v>
       </c>
       <c r="Q93">
-        <v>140.69048145</v>
+        <v>140.5798274</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5845106134275997</v>
+        <v>0.6487369338105675</v>
       </c>
       <c r="T93">
-        <v>7.838895824290296</v>
+        <v>8.77346704325374</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>9.062995370319864</v>
+        <v>8.964484551077257</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08389195470484537</v>
+        <v>0.08353270420120679</v>
       </c>
       <c r="C94">
-        <v>93.95637016023312</v>
+        <v>91.77881157393381</v>
       </c>
       <c r="D94">
-        <v>329.6003701602331</v>
+        <v>330.6048115739338</v>
       </c>
       <c r="E94">
-        <v>264.044</v>
+        <v>267.226</v>
       </c>
       <c r="F94">
-        <v>292.744</v>
+        <v>295.926</v>
       </c>
       <c r="G94">
         <v>57.1</v>
@@ -8995,28 +8995,28 @@
         <v>140.4</v>
       </c>
       <c r="M94">
-        <v>15.661804</v>
+        <v>15.832041</v>
       </c>
       <c r="N94">
-        <v>124.738196</v>
+        <v>124.567959</v>
       </c>
       <c r="O94">
-        <v>43.6583686</v>
+        <v>43.59878565</v>
       </c>
       <c r="P94">
-        <v>81.0798274</v>
+        <v>80.96917335000001</v>
       </c>
       <c r="Q94">
-        <v>140.5798274</v>
+        <v>140.46917335</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6487369338105675</v>
+        <v>0.7313136314458117</v>
       </c>
       <c r="T94">
-        <v>8.77346704325374</v>
+        <v>9.975058610492454</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>8.964484551077257</v>
+        <v>8.868092244076429</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08353270420120679</v>
+        <v>0.08317345369756821</v>
       </c>
       <c r="C95">
-        <v>91.77881157393381</v>
+        <v>89.60739367572756</v>
       </c>
       <c r="D95">
-        <v>330.6048115739338</v>
+        <v>331.6153936757275</v>
       </c>
       <c r="E95">
-        <v>267.226</v>
+        <v>270.408</v>
       </c>
       <c r="F95">
-        <v>295.926</v>
+        <v>299.108</v>
       </c>
       <c r="G95">
         <v>57.1</v>
@@ -9077,28 +9077,28 @@
         <v>140.4</v>
       </c>
       <c r="M95">
-        <v>15.832041</v>
+        <v>16.002278</v>
       </c>
       <c r="N95">
-        <v>124.567959</v>
+        <v>124.397722</v>
       </c>
       <c r="O95">
-        <v>43.59878565</v>
+        <v>43.5392027</v>
       </c>
       <c r="P95">
-        <v>80.96917335000001</v>
+        <v>80.85851930000001</v>
       </c>
       <c r="Q95">
-        <v>140.46917335</v>
+        <v>140.3585193</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7313136314458117</v>
+        <v>0.841415894959471</v>
       </c>
       <c r="T95">
-        <v>9.975058610492454</v>
+        <v>11.57718070014408</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>8.868092244076429</v>
+        <v>8.773750837224551</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08317345369756821</v>
+        <v>0.08281420319392963</v>
       </c>
       <c r="C96">
-        <v>89.60739367572756</v>
+        <v>87.44217295024549</v>
       </c>
       <c r="D96">
-        <v>331.6153936757275</v>
+        <v>332.6321729502455</v>
       </c>
       <c r="E96">
-        <v>270.408</v>
+        <v>273.59</v>
       </c>
       <c r="F96">
-        <v>299.108</v>
+        <v>302.29</v>
       </c>
       <c r="G96">
         <v>57.1</v>
@@ -9159,28 +9159,28 @@
         <v>140.4</v>
       </c>
       <c r="M96">
-        <v>16.002278</v>
+        <v>16.172515</v>
       </c>
       <c r="N96">
-        <v>124.397722</v>
+        <v>124.227485</v>
       </c>
       <c r="O96">
-        <v>43.5392027</v>
+        <v>43.47961975</v>
       </c>
       <c r="P96">
-        <v>80.85851930000001</v>
+        <v>80.74786525</v>
       </c>
       <c r="Q96">
-        <v>140.3585193</v>
+        <v>140.24786525</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.841415894959471</v>
+        <v>0.9955590638785939</v>
       </c>
       <c r="T96">
-        <v>11.57718070014408</v>
+        <v>13.82015162565635</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>8.773750837224551</v>
+        <v>8.681395565253766</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08281420319392963</v>
+        <v>0.08245495269029104</v>
       </c>
       <c r="C97">
-        <v>87.44217295024549</v>
+        <v>85.2832065770084</v>
       </c>
       <c r="D97">
-        <v>332.6321729502455</v>
+        <v>333.6552065770084</v>
       </c>
       <c r="E97">
-        <v>273.59</v>
+        <v>276.772</v>
       </c>
       <c r="F97">
-        <v>302.29</v>
+        <v>305.472</v>
       </c>
       <c r="G97">
         <v>57.1</v>
@@ -9241,28 +9241,28 @@
         <v>140.4</v>
       </c>
       <c r="M97">
-        <v>16.172515</v>
+        <v>16.342752</v>
       </c>
       <c r="N97">
-        <v>124.227485</v>
+        <v>124.057248</v>
       </c>
       <c r="O97">
-        <v>43.47961975</v>
+        <v>43.4200368</v>
       </c>
       <c r="P97">
-        <v>80.74786525</v>
+        <v>80.6372112</v>
       </c>
       <c r="Q97">
-        <v>140.24786525</v>
+        <v>140.1372112</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9955590638785939</v>
+        <v>1.226773817257278</v>
       </c>
       <c r="T97">
-        <v>13.82015162565635</v>
+        <v>17.18460801392475</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>8.681395565253766</v>
+        <v>8.590964361449039</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08245495269029106</v>
+        <v>0.08209570218665248</v>
       </c>
       <c r="C98">
-        <v>85.2832065770084</v>
+        <v>83.13055244114588</v>
       </c>
       <c r="D98">
-        <v>333.6552065770084</v>
+        <v>334.6845524411459</v>
       </c>
       <c r="E98">
-        <v>276.772</v>
+        <v>279.954</v>
       </c>
       <c r="F98">
-        <v>305.472</v>
+        <v>308.654</v>
       </c>
       <c r="G98">
         <v>57.1</v>
@@ -9323,28 +9323,28 @@
         <v>140.4</v>
       </c>
       <c r="M98">
-        <v>16.342752</v>
+        <v>16.512989</v>
       </c>
       <c r="N98">
-        <v>124.057248</v>
+        <v>123.887011</v>
       </c>
       <c r="O98">
-        <v>43.42003680000001</v>
+        <v>43.36045385</v>
       </c>
       <c r="P98">
-        <v>80.63721120000001</v>
+        <v>80.52655715</v>
       </c>
       <c r="Q98">
-        <v>140.1372112</v>
+        <v>140.02655715</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.226773817257276</v>
+        <v>1.612131739555081</v>
       </c>
       <c r="T98">
-        <v>17.18460801392471</v>
+        <v>22.79203532770536</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>8.590964361449041</v>
+        <v>8.502397718547503</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08209570218665248</v>
+        <v>0.08173645168301388</v>
       </c>
       <c r="C99">
-        <v>83.13055244114588</v>
+        <v>80.98426914431417</v>
       </c>
       <c r="D99">
-        <v>334.6845524411459</v>
+        <v>335.7202691443141</v>
       </c>
       <c r="E99">
-        <v>279.954</v>
+        <v>283.136</v>
       </c>
       <c r="F99">
-        <v>308.654</v>
+        <v>311.836</v>
       </c>
       <c r="G99">
         <v>57.1</v>
@@ -9405,28 +9405,28 @@
         <v>140.4</v>
       </c>
       <c r="M99">
-        <v>16.512989</v>
+        <v>16.683226</v>
       </c>
       <c r="N99">
-        <v>123.887011</v>
+        <v>123.716774</v>
       </c>
       <c r="O99">
-        <v>43.36045385</v>
+        <v>43.3008709</v>
       </c>
       <c r="P99">
-        <v>80.52655715</v>
+        <v>80.41590310000001</v>
       </c>
       <c r="Q99">
-        <v>140.02655715</v>
+        <v>139.9159031</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.612131739555081</v>
+        <v>2.382847584150692</v>
       </c>
       <c r="T99">
-        <v>22.79203532770536</v>
+        <v>34.00688995526667</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>8.502397718547503</v>
+        <v>8.415638558154162</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08173645168301388</v>
+        <v>0.0813772011793753</v>
       </c>
       <c r="C100">
-        <v>80.98426914431417</v>
+        <v>78.84441601581682</v>
       </c>
       <c r="D100">
-        <v>335.7202691443141</v>
+        <v>336.7624160158168</v>
       </c>
       <c r="E100">
-        <v>283.136</v>
+        <v>286.318</v>
       </c>
       <c r="F100">
-        <v>311.836</v>
+        <v>315.018</v>
       </c>
       <c r="G100">
         <v>57.1</v>
@@ -9487,28 +9487,28 @@
         <v>140.4</v>
       </c>
       <c r="M100">
-        <v>16.683226</v>
+        <v>16.853463</v>
       </c>
       <c r="N100">
-        <v>123.716774</v>
+        <v>123.546537</v>
       </c>
       <c r="O100">
-        <v>43.3008709</v>
+        <v>43.24128795</v>
       </c>
       <c r="P100">
-        <v>80.41590310000001</v>
+        <v>80.30524905</v>
       </c>
       <c r="Q100">
-        <v>139.9159031</v>
+        <v>139.80524905</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.382847584150692</v>
+        <v>4.694995117937526</v>
       </c>
       <c r="T100">
-        <v>34.00688995526667</v>
+        <v>67.65145383795058</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>8.415638558154162</v>
+        <v>8.330632108071796</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0813772011793753</v>
-      </c>
-      <c r="C101">
-        <v>78.84441601581682</v>
-      </c>
-      <c r="D101">
-        <v>336.7624160158168</v>
-      </c>
-      <c r="E101">
-        <v>286.318</v>
-      </c>
-      <c r="F101">
-        <v>315.018</v>
-      </c>
-      <c r="G101">
-        <v>57.1</v>
-      </c>
-      <c r="H101">
-        <v>289.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>199.9</v>
-      </c>
-      <c r="K101">
-        <v>59.5</v>
-      </c>
-      <c r="L101">
-        <v>140.4</v>
-      </c>
-      <c r="M101">
-        <v>16.853463</v>
-      </c>
-      <c r="N101">
-        <v>123.546537</v>
-      </c>
-      <c r="O101">
-        <v>43.24128795</v>
-      </c>
-      <c r="P101">
-        <v>80.30524905</v>
-      </c>
-      <c r="Q101">
-        <v>139.80524905</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.694995117937526</v>
-      </c>
-      <c r="T101">
-        <v>67.65145383795058</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.034775</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>8.330632108071796</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
